--- a/research/traditional_assets/database/data/latvia/latvia_telecom_equipment.xlsx
+++ b/research/traditional_assets/database/data/latvia/latvia_telecom_equipment.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.115338751039929</v>
+        <v>0.1151440735378491</v>
       </c>
       <c r="C2">
-        <v>17.75144015237601</v>
+        <v>17.61056702010358</v>
       </c>
       <c r="D2">
-        <v>13.33144015237601</v>
+        <v>13.36886702010358</v>
       </c>
       <c r="E2">
-        <v>-1.83</v>
+        <v>-1.6517</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.1783</v>
       </c>
       <c r="G2">
         <v>4.42</v>
@@ -1439,28 +1439,28 @@
         <v>2.278</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.008968489999999999</v>
       </c>
       <c r="N2">
-        <v>2.278</v>
+        <v>2.26903151</v>
       </c>
       <c r="O2">
-        <v>0.4556</v>
+        <v>0.4538063020000001</v>
       </c>
       <c r="P2">
-        <v>1.8224</v>
+        <v>1.815225208</v>
       </c>
       <c r="Q2">
-        <v>1.8644</v>
+        <v>1.857225208</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.115338751039929</v>
+        <v>0.1159006803412617</v>
       </c>
       <c r="T2">
-        <v>1.172523243405601</v>
+        <v>1.181998178705849</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>254.0003947152754</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1151440735378491</v>
+        <v>0.1149493960357692</v>
       </c>
       <c r="C3">
-        <v>17.61056702010358</v>
+        <v>17.4699046248596</v>
       </c>
       <c r="D3">
-        <v>13.36886702010358</v>
+        <v>13.4065046248596</v>
       </c>
       <c r="E3">
-        <v>-1.6517</v>
+        <v>-1.4734</v>
       </c>
       <c r="F3">
-        <v>0.1783</v>
+        <v>0.3566</v>
       </c>
       <c r="G3">
         <v>4.42</v>
@@ -1521,28 +1521,28 @@
         <v>2.278</v>
       </c>
       <c r="M3">
-        <v>0.008968489999999999</v>
+        <v>0.01793698</v>
       </c>
       <c r="N3">
-        <v>2.26903151</v>
+        <v>2.26006302</v>
       </c>
       <c r="O3">
-        <v>0.4538063020000001</v>
+        <v>0.452012604</v>
       </c>
       <c r="P3">
-        <v>1.815225208</v>
+        <v>1.808050416</v>
       </c>
       <c r="Q3">
-        <v>1.857225208</v>
+        <v>1.850050416</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1159006803412617</v>
+        <v>0.1164740775875196</v>
       </c>
       <c r="T3">
-        <v>1.181998178705849</v>
+        <v>1.191666480032632</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>254.0003947152754</v>
+        <v>127.0001973576377</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1149493960357692</v>
+        <v>0.1147547185336894</v>
       </c>
       <c r="C4">
-        <v>17.4699046248596</v>
+        <v>17.32945475154403</v>
       </c>
       <c r="D4">
-        <v>13.4065046248596</v>
+        <v>13.44435475154404</v>
       </c>
       <c r="E4">
-        <v>-1.4734</v>
+        <v>-1.2951</v>
       </c>
       <c r="F4">
-        <v>0.3566</v>
+        <v>0.5348999999999999</v>
       </c>
       <c r="G4">
         <v>4.42</v>
@@ -1603,28 +1603,28 @@
         <v>2.278</v>
       </c>
       <c r="M4">
-        <v>0.01793698</v>
+        <v>0.02690546999999999</v>
       </c>
       <c r="N4">
-        <v>2.26006302</v>
+        <v>2.25109453</v>
       </c>
       <c r="O4">
-        <v>0.452012604</v>
+        <v>0.450218906</v>
       </c>
       <c r="P4">
-        <v>1.808050416</v>
+        <v>1.800875624</v>
       </c>
       <c r="Q4">
-        <v>1.850050416</v>
+        <v>1.842875624</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1164740775875196</v>
+        <v>0.1170592974574117</v>
       </c>
       <c r="T4">
-        <v>1.191666480032632</v>
+        <v>1.201534127778523</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>127.0001973576377</v>
+        <v>84.66679823842514</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1147547185336894</v>
+        <v>0.1145600410316095</v>
       </c>
       <c r="C5">
-        <v>17.32945475154403</v>
+        <v>17.18921920527091</v>
       </c>
       <c r="D5">
-        <v>13.44435475154404</v>
+        <v>13.48241920527091</v>
       </c>
       <c r="E5">
-        <v>-1.2951</v>
+        <v>-1.1168</v>
       </c>
       <c r="F5">
-        <v>0.5348999999999999</v>
+        <v>0.7131999999999999</v>
       </c>
       <c r="G5">
         <v>4.42</v>
@@ -1685,28 +1685,28 @@
         <v>2.278</v>
       </c>
       <c r="M5">
-        <v>0.02690546999999999</v>
+        <v>0.03587396</v>
       </c>
       <c r="N5">
-        <v>2.25109453</v>
+        <v>2.24212604</v>
       </c>
       <c r="O5">
-        <v>0.450218906</v>
+        <v>0.448425208</v>
       </c>
       <c r="P5">
-        <v>1.800875624</v>
+        <v>1.793700832</v>
       </c>
       <c r="Q5">
-        <v>1.842875624</v>
+        <v>1.835700832</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1170592974574117</v>
+        <v>0.1176567094079266</v>
       </c>
       <c r="T5">
-        <v>1.201534127778523</v>
+        <v>1.211607351519122</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>84.66679823842514</v>
+        <v>63.50009867881885</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1145600410316095</v>
+        <v>0.1143653635295297</v>
       </c>
       <c r="C6">
-        <v>17.18921920527091</v>
+        <v>17.04919981165529</v>
       </c>
       <c r="D6">
-        <v>13.48241920527091</v>
+        <v>13.52069981165529</v>
       </c>
       <c r="E6">
-        <v>-1.1168</v>
+        <v>-0.9385000000000001</v>
       </c>
       <c r="F6">
-        <v>0.7131999999999999</v>
+        <v>0.8915</v>
       </c>
       <c r="G6">
         <v>4.42</v>
@@ -1767,28 +1767,28 @@
         <v>2.278</v>
       </c>
       <c r="M6">
-        <v>0.03587396</v>
+        <v>0.04484245</v>
       </c>
       <c r="N6">
-        <v>2.24212604</v>
+        <v>2.23315755</v>
       </c>
       <c r="O6">
-        <v>0.448425208</v>
+        <v>0.44663151</v>
       </c>
       <c r="P6">
-        <v>1.793700832</v>
+        <v>1.78652604</v>
       </c>
       <c r="Q6">
-        <v>1.835700832</v>
+        <v>1.82852604</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1176567094079266</v>
+        <v>0.1182666984521365</v>
       </c>
       <c r="T6">
-        <v>1.211607351519122</v>
+        <v>1.221892643127942</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>63.50009867881885</v>
+        <v>50.80007894305508</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1143653635295297</v>
+        <v>0.1141706860274498</v>
       </c>
       <c r="C7">
-        <v>17.04919981165529</v>
+        <v>16.90939841710512</v>
       </c>
       <c r="D7">
-        <v>13.52069981165529</v>
+        <v>13.55919841710512</v>
       </c>
       <c r="E7">
-        <v>-0.9385000000000001</v>
+        <v>-0.7602</v>
       </c>
       <c r="F7">
-        <v>0.8915</v>
+        <v>1.0698</v>
       </c>
       <c r="G7">
         <v>4.42</v>
@@ -1849,28 +1849,28 @@
         <v>2.278</v>
       </c>
       <c r="M7">
-        <v>0.04484245</v>
+        <v>0.05381094</v>
       </c>
       <c r="N7">
-        <v>2.23315755</v>
+        <v>2.22418906</v>
       </c>
       <c r="O7">
-        <v>0.44663151</v>
+        <v>0.4448378120000001</v>
       </c>
       <c r="P7">
-        <v>1.78652604</v>
+        <v>1.779351248</v>
       </c>
       <c r="Q7">
-        <v>1.82852604</v>
+        <v>1.821351248</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1182666984521365</v>
+        <v>0.1188896659866487</v>
       </c>
       <c r="T7">
-        <v>1.221892643127942</v>
+        <v>1.232396770728441</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>50.80007894305508</v>
+        <v>42.33339911921256</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1141706860274498</v>
+        <v>0.1139760085253699</v>
       </c>
       <c r="C8">
-        <v>16.90939841710512</v>
+        <v>16.76981688911811</v>
       </c>
       <c r="D8">
-        <v>13.55919841710512</v>
+        <v>13.59791688911811</v>
       </c>
       <c r="E8">
-        <v>-0.7602000000000002</v>
+        <v>-0.5819000000000003</v>
       </c>
       <c r="F8">
-        <v>1.0698</v>
+        <v>1.2481</v>
       </c>
       <c r="G8">
         <v>4.42</v>
@@ -1931,28 +1931,28 @@
         <v>2.278</v>
       </c>
       <c r="M8">
-        <v>0.05381093999999999</v>
+        <v>0.06277942999999998</v>
       </c>
       <c r="N8">
-        <v>2.22418906</v>
+        <v>2.21522057</v>
       </c>
       <c r="O8">
-        <v>0.4448378120000001</v>
+        <v>0.443044114</v>
       </c>
       <c r="P8">
-        <v>1.779351248</v>
+        <v>1.772176456</v>
       </c>
       <c r="Q8">
-        <v>1.821351248</v>
+        <v>1.814176456</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1188896659866487</v>
+        <v>0.1195260306724408</v>
       </c>
       <c r="T8">
-        <v>1.232396770728441</v>
+        <v>1.243126793546154</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>42.33339911921257</v>
+        <v>36.28577067361078</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1139760085253699</v>
+        <v>0.1137813310232901</v>
       </c>
       <c r="C9">
-        <v>16.76981688911811</v>
+        <v>16.63045711658373</v>
       </c>
       <c r="D9">
-        <v>13.59791688911812</v>
+        <v>13.63685711658373</v>
       </c>
       <c r="E9">
-        <v>-0.5819000000000001</v>
+        <v>-0.4036000000000002</v>
       </c>
       <c r="F9">
-        <v>1.2481</v>
+        <v>1.4264</v>
       </c>
       <c r="G9">
         <v>4.42</v>
@@ -2013,28 +2013,28 @@
         <v>2.278</v>
       </c>
       <c r="M9">
-        <v>0.06277943</v>
+        <v>0.07174791999999999</v>
       </c>
       <c r="N9">
-        <v>2.21522057</v>
+        <v>2.20625208</v>
       </c>
       <c r="O9">
-        <v>0.443044114</v>
+        <v>0.441250416</v>
       </c>
       <c r="P9">
-        <v>1.772176456</v>
+        <v>1.765001664</v>
       </c>
       <c r="Q9">
-        <v>1.814176456</v>
+        <v>1.807001664</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1195260306724408</v>
+        <v>0.1201762293731414</v>
       </c>
       <c r="T9">
-        <v>1.243126793546154</v>
+        <v>1.254090077729469</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>36.28577067361077</v>
+        <v>31.75004933940943</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1137813310232901</v>
+        <v>0.1135866535212102</v>
       </c>
       <c r="C10">
-        <v>16.63045711658373</v>
+        <v>16.49132101009038</v>
       </c>
       <c r="D10">
-        <v>13.63685711658373</v>
+        <v>13.67602101009038</v>
       </c>
       <c r="E10">
-        <v>-0.4036000000000002</v>
+        <v>-0.2253000000000003</v>
       </c>
       <c r="F10">
-        <v>1.4264</v>
+        <v>1.6047</v>
       </c>
       <c r="G10">
         <v>4.42</v>
@@ -2095,28 +2095,28 @@
         <v>2.278</v>
       </c>
       <c r="M10">
-        <v>0.07174791999999999</v>
+        <v>0.08071640999999999</v>
       </c>
       <c r="N10">
-        <v>2.20625208</v>
+        <v>2.19728359</v>
       </c>
       <c r="O10">
-        <v>0.441250416</v>
+        <v>0.439456718</v>
       </c>
       <c r="P10">
-        <v>1.765001664</v>
+        <v>1.757826872</v>
       </c>
       <c r="Q10">
-        <v>1.807001664</v>
+        <v>1.799826872</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1201762293731414</v>
+        <v>0.1208407181551761</v>
       </c>
       <c r="T10">
-        <v>1.254090077729469</v>
+        <v>1.265294313213517</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>31.75004933940943</v>
+        <v>28.22226607947504</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1135866535212102</v>
+        <v>0.1133919760191304</v>
       </c>
       <c r="C11">
-        <v>16.49132101009038</v>
+        <v>16.35241050223783</v>
       </c>
       <c r="D11">
-        <v>13.67602101009038</v>
+        <v>13.71541050223783</v>
       </c>
       <c r="E11">
-        <v>-0.2253000000000003</v>
+        <v>-0.04700000000000037</v>
       </c>
       <c r="F11">
-        <v>1.6047</v>
+        <v>1.783</v>
       </c>
       <c r="G11">
         <v>4.42</v>
@@ -2177,28 +2177,28 @@
         <v>2.278</v>
       </c>
       <c r="M11">
-        <v>0.08071640999999999</v>
+        <v>0.08968489999999998</v>
       </c>
       <c r="N11">
-        <v>2.19728359</v>
+        <v>2.1883151</v>
       </c>
       <c r="O11">
-        <v>0.439456718</v>
+        <v>0.43766302</v>
       </c>
       <c r="P11">
-        <v>1.757826872</v>
+        <v>1.75065208</v>
       </c>
       <c r="Q11">
-        <v>1.799826872</v>
+        <v>1.79265208</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1208407181551761</v>
+        <v>0.1215199733545893</v>
       </c>
       <c r="T11">
-        <v>1.265294313213517</v>
+        <v>1.276747531708321</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>28.22226607947504</v>
+        <v>25.40003947152754</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1133919760191304</v>
+        <v>0.1131972985170505</v>
       </c>
       <c r="C12">
-        <v>16.35241050223783</v>
+        <v>16.21372754795517</v>
       </c>
       <c r="D12">
-        <v>13.71541050223783</v>
+        <v>13.75502754795518</v>
       </c>
       <c r="E12">
-        <v>-0.04700000000000015</v>
+        <v>0.1312999999999998</v>
       </c>
       <c r="F12">
-        <v>1.783</v>
+        <v>1.9613</v>
       </c>
       <c r="G12">
         <v>4.42</v>
@@ -2259,28 +2259,28 @@
         <v>2.278</v>
       </c>
       <c r="M12">
-        <v>0.0896849</v>
+        <v>0.09865338999999998</v>
       </c>
       <c r="N12">
-        <v>2.1883151</v>
+        <v>2.17934661</v>
       </c>
       <c r="O12">
-        <v>0.43766302</v>
+        <v>0.4358693220000001</v>
       </c>
       <c r="P12">
-        <v>1.75065208</v>
+        <v>1.743477288</v>
       </c>
       <c r="Q12">
-        <v>1.79265208</v>
+        <v>1.785477288</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1215199733545893</v>
+        <v>0.1222144927157871</v>
       </c>
       <c r="T12">
-        <v>1.276747531708322</v>
+        <v>1.288458125899638</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>25.40003947152754</v>
+        <v>23.09094497411595</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1131972985170505</v>
+        <v>0.1130026210149707</v>
       </c>
       <c r="C13">
-        <v>16.21372754795517</v>
+        <v>16.07527412482424</v>
       </c>
       <c r="D13">
-        <v>13.75502754795518</v>
+        <v>13.79487412482424</v>
       </c>
       <c r="E13">
-        <v>0.1312999999999998</v>
+        <v>0.3095999999999997</v>
       </c>
       <c r="F13">
-        <v>1.9613</v>
+        <v>2.1396</v>
       </c>
       <c r="G13">
         <v>4.42</v>
@@ -2341,28 +2341,28 @@
         <v>2.278</v>
       </c>
       <c r="M13">
-        <v>0.09865338999999998</v>
+        <v>0.10762188</v>
       </c>
       <c r="N13">
-        <v>2.17934661</v>
+        <v>2.17037812</v>
       </c>
       <c r="O13">
-        <v>0.4358693220000001</v>
+        <v>0.434075624</v>
       </c>
       <c r="P13">
-        <v>1.743477288</v>
+        <v>1.736302496</v>
       </c>
       <c r="Q13">
-        <v>1.785477288</v>
+        <v>1.778302496</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1222144927157871</v>
+        <v>0.1229247966079212</v>
       </c>
       <c r="T13">
-        <v>1.288458125899638</v>
+        <v>1.30043486995894</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>23.09094497411595</v>
+        <v>21.16669955960629</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1130026210149707</v>
+        <v>0.1128079435128908</v>
       </c>
       <c r="C14">
-        <v>16.07527412482424</v>
+        <v>15.93705223340863</v>
       </c>
       <c r="D14">
-        <v>13.79487412482424</v>
+        <v>13.83495223340863</v>
       </c>
       <c r="E14">
-        <v>0.3095999999999997</v>
+        <v>0.4878999999999998</v>
       </c>
       <c r="F14">
-        <v>2.1396</v>
+        <v>2.3179</v>
       </c>
       <c r="G14">
         <v>4.42</v>
@@ -2423,28 +2423,28 @@
         <v>2.278</v>
       </c>
       <c r="M14">
-        <v>0.10762188</v>
+        <v>0.11659037</v>
       </c>
       <c r="N14">
-        <v>2.17037812</v>
+        <v>2.16140963</v>
       </c>
       <c r="O14">
-        <v>0.434075624</v>
+        <v>0.432281926</v>
       </c>
       <c r="P14">
-        <v>1.736302496</v>
+        <v>1.729127704</v>
       </c>
       <c r="Q14">
-        <v>1.778302496</v>
+        <v>1.771127704</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1229247966079212</v>
+        <v>0.1236514293251618</v>
       </c>
       <c r="T14">
-        <v>1.30043486995894</v>
+        <v>1.31268694146788</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>21.16669955960629</v>
+        <v>19.53849190117503</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1128079435128908</v>
+        <v>0.1126132660108109</v>
       </c>
       <c r="C15">
-        <v>15.93705223340863</v>
+        <v>15.7990638975886</v>
       </c>
       <c r="D15">
-        <v>13.83495223340863</v>
+        <v>13.8752638975886</v>
       </c>
       <c r="E15">
-        <v>0.4878999999999998</v>
+        <v>0.6661999999999999</v>
       </c>
       <c r="F15">
-        <v>2.3179</v>
+        <v>2.4962</v>
       </c>
       <c r="G15">
         <v>4.42</v>
@@ -2505,28 +2505,28 @@
         <v>2.278</v>
       </c>
       <c r="M15">
-        <v>0.11659037</v>
+        <v>0.12555886</v>
       </c>
       <c r="N15">
-        <v>2.16140963</v>
+        <v>2.15244114</v>
       </c>
       <c r="O15">
-        <v>0.432281926</v>
+        <v>0.430488228</v>
       </c>
       <c r="P15">
-        <v>1.729127704</v>
+        <v>1.721952912</v>
       </c>
       <c r="Q15">
-        <v>1.771127704</v>
+        <v>1.763952912</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1236514293251618</v>
+        <v>0.1243949604776871</v>
       </c>
       <c r="T15">
-        <v>1.31268694146788</v>
+        <v>1.325223944872377</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>19.53849190117503</v>
+        <v>18.14288533680539</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1126132660108109</v>
+        <v>0.1124185885087311</v>
       </c>
       <c r="C16">
-        <v>15.7990638975886</v>
+        <v>15.66131116490164</v>
       </c>
       <c r="D16">
-        <v>13.8752638975886</v>
+        <v>13.91581116490164</v>
       </c>
       <c r="E16">
-        <v>0.6661999999999999</v>
+        <v>0.8445</v>
       </c>
       <c r="F16">
-        <v>2.4962</v>
+        <v>2.6745</v>
       </c>
       <c r="G16">
         <v>4.42</v>
@@ -2587,28 +2587,28 @@
         <v>2.278</v>
       </c>
       <c r="M16">
-        <v>0.12555886</v>
+        <v>0.13452735</v>
       </c>
       <c r="N16">
-        <v>2.15244114</v>
+        <v>2.14347265</v>
       </c>
       <c r="O16">
-        <v>0.430488228</v>
+        <v>0.42869453</v>
       </c>
       <c r="P16">
-        <v>1.721952912</v>
+        <v>1.71477812</v>
       </c>
       <c r="Q16">
-        <v>1.763952912</v>
+        <v>1.75677812</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1243949604776871</v>
+        <v>0.1251559864808601</v>
       </c>
       <c r="T16">
-        <v>1.325223944872377</v>
+        <v>1.338055936592275</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>18.14288533680539</v>
+        <v>16.93335964768503</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1124185885087311</v>
+        <v>0.1122239110066512</v>
       </c>
       <c r="C17">
-        <v>15.66131116490164</v>
+        <v>15.52379610688928</v>
       </c>
       <c r="D17">
-        <v>13.91581116490164</v>
+        <v>13.95659610688928</v>
       </c>
       <c r="E17">
-        <v>0.8444999999999996</v>
+        <v>1.0228</v>
       </c>
       <c r="F17">
-        <v>2.6745</v>
+        <v>2.8528</v>
       </c>
       <c r="G17">
         <v>4.42</v>
@@ -2669,28 +2669,28 @@
         <v>2.278</v>
       </c>
       <c r="M17">
-        <v>0.13452735</v>
+        <v>0.14349584</v>
       </c>
       <c r="N17">
-        <v>2.14347265</v>
+        <v>2.13450416</v>
       </c>
       <c r="O17">
-        <v>0.42869453</v>
+        <v>0.4269008320000001</v>
       </c>
       <c r="P17">
-        <v>1.71477812</v>
+        <v>1.707603328</v>
       </c>
       <c r="Q17">
-        <v>1.75677812</v>
+        <v>1.749603328</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1251559864808601</v>
+        <v>0.1259351321507753</v>
       </c>
       <c r="T17">
-        <v>1.338055936592275</v>
+        <v>1.35119345192455</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>16.93335964768503</v>
+        <v>15.87502466970471</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1122239110066512</v>
+        <v>0.1120292335045714</v>
       </c>
       <c r="C18">
-        <v>15.52379610688928</v>
+        <v>15.38652081944977</v>
       </c>
       <c r="D18">
-        <v>13.95659610688928</v>
+        <v>13.99762081944977</v>
       </c>
       <c r="E18">
-        <v>1.0228</v>
+        <v>1.2011</v>
       </c>
       <c r="F18">
-        <v>2.8528</v>
+        <v>3.0311</v>
       </c>
       <c r="G18">
         <v>4.42</v>
@@ -2751,28 +2751,28 @@
         <v>2.278</v>
       </c>
       <c r="M18">
-        <v>0.14349584</v>
+        <v>0.15246433</v>
       </c>
       <c r="N18">
-        <v>2.13450416</v>
+        <v>2.12553567</v>
       </c>
       <c r="O18">
-        <v>0.4269008320000001</v>
+        <v>0.4251071340000001</v>
       </c>
       <c r="P18">
-        <v>1.707603328</v>
+        <v>1.700428536</v>
       </c>
       <c r="Q18">
-        <v>1.749603328</v>
+        <v>1.742428536</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1259351321507753</v>
+        <v>0.1267330524151462</v>
       </c>
       <c r="T18">
-        <v>1.35119345192455</v>
+        <v>1.364647533891338</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>15.87502466970471</v>
+        <v>14.94119968913385</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1120292335045714</v>
+        <v>0.1118345560024915</v>
       </c>
       <c r="C19">
-        <v>15.38652081944977</v>
+        <v>15.24948742319718</v>
       </c>
       <c r="D19">
-        <v>13.99762081944977</v>
+        <v>14.03888742319718</v>
       </c>
       <c r="E19">
-        <v>1.2011</v>
+        <v>1.3794</v>
       </c>
       <c r="F19">
-        <v>3.0311</v>
+        <v>3.2094</v>
       </c>
       <c r="G19">
         <v>4.42</v>
@@ -2833,28 +2833,28 @@
         <v>2.278</v>
       </c>
       <c r="M19">
-        <v>0.15246433</v>
+        <v>0.16143282</v>
       </c>
       <c r="N19">
-        <v>2.12553567</v>
+        <v>2.11656718</v>
       </c>
       <c r="O19">
-        <v>0.4251071340000001</v>
+        <v>0.423313436</v>
       </c>
       <c r="P19">
-        <v>1.700428536</v>
+        <v>1.693253744</v>
       </c>
       <c r="Q19">
-        <v>1.742428536</v>
+        <v>1.735253744</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1267330524151462</v>
+        <v>0.1275504341493799</v>
       </c>
       <c r="T19">
-        <v>1.364647533891338</v>
+        <v>1.37842976419878</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>14.94119968913385</v>
+        <v>14.11113303973752</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1118345560024915</v>
+        <v>0.1116398785004117</v>
       </c>
       <c r="C20">
-        <v>15.24948742319718</v>
+        <v>15.1126980638268</v>
       </c>
       <c r="D20">
-        <v>14.03888742319718</v>
+        <v>14.0803980638268</v>
       </c>
       <c r="E20">
-        <v>1.3794</v>
+        <v>1.5577</v>
       </c>
       <c r="F20">
-        <v>3.2094</v>
+        <v>3.3877</v>
       </c>
       <c r="G20">
         <v>4.42</v>
@@ -2915,28 +2915,28 @@
         <v>2.278</v>
       </c>
       <c r="M20">
-        <v>0.16143282</v>
+        <v>0.17040131</v>
       </c>
       <c r="N20">
-        <v>2.11656718</v>
+        <v>2.10759869</v>
       </c>
       <c r="O20">
-        <v>0.423313436</v>
+        <v>0.421519738</v>
       </c>
       <c r="P20">
-        <v>1.693253744</v>
+        <v>1.686078952</v>
       </c>
       <c r="Q20">
-        <v>1.735253744</v>
+        <v>1.728078952</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1275504341493799</v>
+        <v>0.1283879981486564</v>
       </c>
       <c r="T20">
-        <v>1.37842976419878</v>
+        <v>1.392552296489122</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>14.11113303973752</v>
+        <v>13.36844182711976</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1116398785004117</v>
+        <v>0.1116852009983318</v>
       </c>
       <c r="C21">
-        <v>15.1126980638268</v>
+        <v>14.92471214343356</v>
       </c>
       <c r="D21">
-        <v>14.0803980638268</v>
+        <v>14.07071214343356</v>
       </c>
       <c r="E21">
-        <v>1.5577</v>
+        <v>1.736</v>
       </c>
       <c r="F21">
-        <v>3.3877</v>
+        <v>3.566</v>
       </c>
       <c r="G21">
         <v>4.42</v>
@@ -2997,45 +2997,45 @@
         <v>2.278</v>
       </c>
       <c r="M21">
-        <v>0.17040131</v>
+        <v>0.1847188</v>
       </c>
       <c r="N21">
-        <v>2.10759869</v>
+        <v>2.0932812</v>
       </c>
       <c r="O21">
-        <v>0.421519738</v>
+        <v>0.41865624</v>
       </c>
       <c r="P21">
-        <v>1.686078952</v>
+        <v>1.67462496</v>
       </c>
       <c r="Q21">
-        <v>1.728078952</v>
+        <v>1.71662496</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1283879981486564</v>
+        <v>0.1292465012479148</v>
       </c>
       <c r="T21">
-        <v>1.392552296489122</v>
+        <v>1.407027892086722</v>
       </c>
       <c r="U21">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V21">
         <v>0.2</v>
       </c>
       <c r="W21">
-        <v>0.04024</v>
+        <v>0.04144</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y21">
-        <v>13.36844182711976</v>
+        <v>12.3322585465042</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1116852009983318</v>
+        <v>0.1115025234962519</v>
       </c>
       <c r="C22">
-        <v>14.92471214343356</v>
+        <v>14.78553396722461</v>
       </c>
       <c r="D22">
-        <v>14.07071214343356</v>
+        <v>14.1098339672246</v>
       </c>
       <c r="E22">
-        <v>1.736</v>
+        <v>1.9143</v>
       </c>
       <c r="F22">
-        <v>3.566</v>
+        <v>3.7443</v>
       </c>
       <c r="G22">
         <v>4.42</v>
@@ -3079,28 +3079,28 @@
         <v>2.278</v>
       </c>
       <c r="M22">
-        <v>0.1847188</v>
+        <v>0.19395474</v>
       </c>
       <c r="N22">
-        <v>2.0932812</v>
+        <v>2.08404526</v>
       </c>
       <c r="O22">
-        <v>0.41865624</v>
+        <v>0.416809052</v>
       </c>
       <c r="P22">
-        <v>1.67462496</v>
+        <v>1.667236208</v>
       </c>
       <c r="Q22">
-        <v>1.71662496</v>
+        <v>1.709236208</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1292465012479148</v>
+        <v>0.1301267386028506</v>
       </c>
       <c r="T22">
-        <v>1.407027892086722</v>
+        <v>1.421869958458944</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>12.3322585465042</v>
+        <v>11.74500813952781</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1115025234962519</v>
+        <v>0.1113198459941721</v>
       </c>
       <c r="C23">
-        <v>14.78553396722461</v>
+        <v>14.64657394406343</v>
       </c>
       <c r="D23">
-        <v>14.1098339672246</v>
+        <v>14.14917394406343</v>
       </c>
       <c r="E23">
-        <v>1.914299999999999</v>
+        <v>2.0926</v>
       </c>
       <c r="F23">
-        <v>3.7443</v>
+        <v>3.9226</v>
       </c>
       <c r="G23">
         <v>4.42</v>
@@ -3161,28 +3161,28 @@
         <v>2.278</v>
       </c>
       <c r="M23">
-        <v>0.19395474</v>
+        <v>0.20319068</v>
       </c>
       <c r="N23">
-        <v>2.08404526</v>
+        <v>2.07480932</v>
       </c>
       <c r="O23">
-        <v>0.416809052</v>
+        <v>0.414961864</v>
       </c>
       <c r="P23">
-        <v>1.667236208</v>
+        <v>1.659847456</v>
       </c>
       <c r="Q23">
-        <v>1.709236208</v>
+        <v>1.701847456</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1301267386028506</v>
+        <v>0.1310295461463745</v>
       </c>
       <c r="T23">
-        <v>1.421869958458944</v>
+        <v>1.437092590635583</v>
       </c>
       <c r="U23">
         <v>0.0518</v>
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>11.74500813952781</v>
+        <v>11.21114413318564</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1113198459941721</v>
+        <v>0.1111371684920923</v>
       </c>
       <c r="C24">
-        <v>14.64657394406343</v>
+        <v>14.5078339037655</v>
       </c>
       <c r="D24">
-        <v>14.14917394406343</v>
+        <v>14.1887339037655</v>
       </c>
       <c r="E24">
-        <v>2.0926</v>
+        <v>2.2709</v>
       </c>
       <c r="F24">
-        <v>3.9226</v>
+        <v>4.1009</v>
       </c>
       <c r="G24">
         <v>4.42</v>
@@ -3243,28 +3243,28 @@
         <v>2.278</v>
       </c>
       <c r="M24">
-        <v>0.20319068</v>
+        <v>0.21242662</v>
       </c>
       <c r="N24">
-        <v>2.07480932</v>
+        <v>2.06557338</v>
       </c>
       <c r="O24">
-        <v>0.414961864</v>
+        <v>0.413114676</v>
       </c>
       <c r="P24">
-        <v>1.659847456</v>
+        <v>1.652458704</v>
       </c>
       <c r="Q24">
-        <v>1.701847456</v>
+        <v>1.694458704</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1310295461463745</v>
+        <v>0.1319558032364834</v>
       </c>
       <c r="T24">
-        <v>1.437092590635583</v>
+        <v>1.452710615855771</v>
       </c>
       <c r="U24">
         <v>0.0518</v>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>11.21114413318564</v>
+        <v>10.72370308391669</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1111371684920923</v>
+        <v>0.1109544909900124</v>
       </c>
       <c r="C25">
-        <v>14.5078339037655</v>
+        <v>14.36931569666774</v>
       </c>
       <c r="D25">
-        <v>14.1887339037655</v>
+        <v>14.22851569666774</v>
       </c>
       <c r="E25">
-        <v>2.2709</v>
+        <v>2.4492</v>
       </c>
       <c r="F25">
-        <v>4.1009</v>
+        <v>4.2792</v>
       </c>
       <c r="G25">
         <v>4.42</v>
@@ -3325,28 +3325,28 @@
         <v>2.278</v>
       </c>
       <c r="M25">
-        <v>0.21242662</v>
+        <v>0.22166256</v>
       </c>
       <c r="N25">
-        <v>2.06557338</v>
+        <v>2.05633744</v>
       </c>
       <c r="O25">
-        <v>0.413114676</v>
+        <v>0.411267488</v>
       </c>
       <c r="P25">
-        <v>1.652458704</v>
+        <v>1.645069952</v>
       </c>
       <c r="Q25">
-        <v>1.694458704</v>
+        <v>1.687069952</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1319558032364834</v>
+        <v>0.1329064355131742</v>
       </c>
       <c r="T25">
-        <v>1.452710615855771</v>
+        <v>1.468739641739648</v>
       </c>
       <c r="U25">
         <v>0.0518</v>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>10.72370308391669</v>
+        <v>10.27688212208683</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1109544909900124</v>
+        <v>0.1107718134879325</v>
       </c>
       <c r="C26">
-        <v>14.36931569666775</v>
+        <v>14.23102119391701</v>
       </c>
       <c r="D26">
-        <v>14.22851569666775</v>
+        <v>14.26852119391701</v>
       </c>
       <c r="E26">
-        <v>2.449199999999999</v>
+        <v>2.6275</v>
       </c>
       <c r="F26">
-        <v>4.279199999999999</v>
+        <v>4.4575</v>
       </c>
       <c r="G26">
         <v>4.42</v>
@@ -3407,28 +3407,28 @@
         <v>2.278</v>
       </c>
       <c r="M26">
-        <v>0.22166256</v>
+        <v>0.2308985</v>
       </c>
       <c r="N26">
-        <v>2.05633744</v>
+        <v>2.0471015</v>
       </c>
       <c r="O26">
-        <v>0.411267488</v>
+        <v>0.4094203000000001</v>
       </c>
       <c r="P26">
-        <v>1.645069952</v>
+        <v>1.6376812</v>
       </c>
       <c r="Q26">
-        <v>1.687069952</v>
+        <v>1.6796812</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1329064355131742</v>
+        <v>0.13388241798391</v>
       </c>
       <c r="T26">
-        <v>1.468739641739648</v>
+        <v>1.485196108313762</v>
       </c>
       <c r="U26">
         <v>0.0518</v>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>10.27688212208684</v>
+        <v>9.865806837203362</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1107718134879325</v>
+        <v>0.1109427359858526</v>
       </c>
       <c r="C27">
-        <v>14.23102119391701</v>
+        <v>14.01528323176847</v>
       </c>
       <c r="D27">
-        <v>14.26852119391701</v>
+        <v>14.23108323176848</v>
       </c>
       <c r="E27">
-        <v>2.6275</v>
+        <v>2.8058</v>
       </c>
       <c r="F27">
-        <v>4.4575</v>
+        <v>4.6358</v>
       </c>
       <c r="G27">
         <v>4.42</v>
@@ -3489,45 +3489,45 @@
         <v>2.278</v>
       </c>
       <c r="M27">
-        <v>0.2308985</v>
+        <v>0.2480153</v>
       </c>
       <c r="N27">
-        <v>2.0471015</v>
+        <v>2.0299847</v>
       </c>
       <c r="O27">
-        <v>0.4094203000000001</v>
+        <v>0.40599694</v>
       </c>
       <c r="P27">
-        <v>1.6376812</v>
+        <v>1.62398776</v>
       </c>
       <c r="Q27">
-        <v>1.6796812</v>
+        <v>1.66598776</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.13388241798391</v>
+        <v>0.1348847783592603</v>
       </c>
       <c r="T27">
-        <v>1.485196108313762</v>
+        <v>1.502097344254743</v>
       </c>
       <c r="U27">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V27">
         <v>0.2</v>
       </c>
       <c r="W27">
-        <v>0.04144</v>
+        <v>0.0428</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y27">
-        <v>9.865806837203362</v>
+        <v>9.184917220832748</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1109427359858526</v>
+        <v>0.1107736584837728</v>
       </c>
       <c r="C28">
-        <v>14.01528323176847</v>
+        <v>13.87401602414723</v>
       </c>
       <c r="D28">
-        <v>14.23108323176848</v>
+        <v>14.26811602414723</v>
       </c>
       <c r="E28">
-        <v>2.8058</v>
+        <v>2.9841</v>
       </c>
       <c r="F28">
-        <v>4.6358</v>
+        <v>4.8141</v>
       </c>
       <c r="G28">
         <v>4.42</v>
@@ -3571,28 +3571,28 @@
         <v>2.278</v>
       </c>
       <c r="M28">
-        <v>0.2480153</v>
+        <v>0.25755435</v>
       </c>
       <c r="N28">
-        <v>2.0299847</v>
+        <v>2.02044565</v>
       </c>
       <c r="O28">
-        <v>0.40599694</v>
+        <v>0.40408913</v>
       </c>
       <c r="P28">
-        <v>1.62398776</v>
+        <v>1.61635652</v>
       </c>
       <c r="Q28">
-        <v>1.66598776</v>
+        <v>1.65835652</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1348847783592603</v>
+        <v>0.1359146006627025</v>
       </c>
       <c r="T28">
-        <v>1.502097344254743</v>
+        <v>1.519461627755752</v>
       </c>
       <c r="U28">
         <v>0.0535</v>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>9.184917220832748</v>
+        <v>8.844735101542646</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1107736584837728</v>
+        <v>0.1106045809816929</v>
       </c>
       <c r="C29">
-        <v>13.87401602414723</v>
+        <v>13.73294205632279</v>
       </c>
       <c r="D29">
-        <v>14.26811602414723</v>
+        <v>14.3053420563228</v>
       </c>
       <c r="E29">
-        <v>2.9841</v>
+        <v>3.1624</v>
       </c>
       <c r="F29">
-        <v>4.8141</v>
+        <v>4.9924</v>
       </c>
       <c r="G29">
         <v>4.42</v>
@@ -3653,28 +3653,28 @@
         <v>2.278</v>
       </c>
       <c r="M29">
-        <v>0.25755435</v>
+        <v>0.2670934</v>
       </c>
       <c r="N29">
-        <v>2.02044565</v>
+        <v>2.0109066</v>
       </c>
       <c r="O29">
-        <v>0.40408913</v>
+        <v>0.4021813200000001</v>
       </c>
       <c r="P29">
-        <v>1.61635652</v>
+        <v>1.60872528</v>
       </c>
       <c r="Q29">
-        <v>1.65835652</v>
+        <v>1.65072528</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1359146006627025</v>
+        <v>0.1369730291412402</v>
       </c>
       <c r="T29">
-        <v>1.519461627755752</v>
+        <v>1.537308252465122</v>
       </c>
       <c r="U29">
         <v>0.0535</v>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>8.844735101542646</v>
+        <v>8.52885170505898</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1106045809816929</v>
+        <v>0.1104355034796131</v>
       </c>
       <c r="C30">
-        <v>13.73294205632279</v>
+        <v>13.59206284476059</v>
       </c>
       <c r="D30">
-        <v>14.3053420563228</v>
+        <v>14.34276284476059</v>
       </c>
       <c r="E30">
-        <v>3.1624</v>
+        <v>3.3407</v>
       </c>
       <c r="F30">
-        <v>4.9924</v>
+        <v>5.1707</v>
       </c>
       <c r="G30">
         <v>4.42</v>
@@ -3735,28 +3735,28 @@
         <v>2.278</v>
       </c>
       <c r="M30">
-        <v>0.2670934</v>
+        <v>0.27663245</v>
       </c>
       <c r="N30">
-        <v>2.0109066</v>
+        <v>2.00136755</v>
       </c>
       <c r="O30">
-        <v>0.4021813200000001</v>
+        <v>0.40027351</v>
       </c>
       <c r="P30">
-        <v>1.60872528</v>
+        <v>1.60109404</v>
       </c>
       <c r="Q30">
-        <v>1.65072528</v>
+        <v>1.64309404</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1369730291412402</v>
+        <v>0.1380612725064973</v>
       </c>
       <c r="T30">
-        <v>1.537308252465122</v>
+        <v>1.555657598997291</v>
       </c>
       <c r="U30">
         <v>0.0535</v>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>8.52885170505898</v>
+        <v>8.234753370401773</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1104355034796131</v>
+        <v>0.1102664259775332</v>
       </c>
       <c r="C31">
-        <v>13.59206284476059</v>
+        <v>13.45137992183511</v>
       </c>
       <c r="D31">
-        <v>14.34276284476059</v>
+        <v>14.38037992183511</v>
       </c>
       <c r="E31">
-        <v>3.340699999999999</v>
+        <v>3.518999999999999</v>
       </c>
       <c r="F31">
-        <v>5.170699999999999</v>
+        <v>5.348999999999999</v>
       </c>
       <c r="G31">
         <v>4.42</v>
@@ -3817,28 +3817,28 @@
         <v>2.278</v>
       </c>
       <c r="M31">
-        <v>0.27663245</v>
+        <v>0.2861715</v>
       </c>
       <c r="N31">
-        <v>2.00136755</v>
+        <v>1.9918285</v>
       </c>
       <c r="O31">
-        <v>0.40027351</v>
+        <v>0.3983657</v>
       </c>
       <c r="P31">
-        <v>1.60109404</v>
+        <v>1.5934628</v>
       </c>
       <c r="Q31">
-        <v>1.64309404</v>
+        <v>1.6354628</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1380612725064973</v>
+        <v>0.1391806085393332</v>
       </c>
       <c r="T31">
-        <v>1.555657598997291</v>
+        <v>1.574531212573236</v>
       </c>
       <c r="U31">
         <v>0.0535</v>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>8.234753370401773</v>
+        <v>7.960261591388382</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1102664259775332</v>
+        <v>0.1100973484754534</v>
       </c>
       <c r="C32">
-        <v>13.45137992183511</v>
+        <v>13.3108948360391</v>
       </c>
       <c r="D32">
-        <v>14.38037992183511</v>
+        <v>14.4181948360391</v>
       </c>
       <c r="E32">
-        <v>3.518999999999999</v>
+        <v>3.697299999999999</v>
       </c>
       <c r="F32">
-        <v>5.348999999999999</v>
+        <v>5.527299999999999</v>
       </c>
       <c r="G32">
         <v>4.42</v>
@@ -3899,28 +3899,28 @@
         <v>2.278</v>
       </c>
       <c r="M32">
-        <v>0.2861715</v>
+        <v>0.29571055</v>
       </c>
       <c r="N32">
-        <v>1.9918285</v>
+        <v>1.98228945</v>
       </c>
       <c r="O32">
-        <v>0.3983657</v>
+        <v>0.39645789</v>
       </c>
       <c r="P32">
-        <v>1.5934628</v>
+        <v>1.58583156</v>
       </c>
       <c r="Q32">
-        <v>1.6354628</v>
+        <v>1.62783156</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1391806085393332</v>
+        <v>0.14033238909486</v>
       </c>
       <c r="T32">
-        <v>1.574531212573236</v>
+        <v>1.593951887412252</v>
       </c>
       <c r="U32">
         <v>0.0535</v>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>7.960261591388382</v>
+        <v>7.703478959408112</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1100973484754534</v>
+        <v>0.1101330709733735</v>
       </c>
       <c r="C33">
-        <v>13.3108948360391</v>
+        <v>13.12458878367366</v>
       </c>
       <c r="D33">
-        <v>14.4181948360391</v>
+        <v>14.41018878367366</v>
       </c>
       <c r="E33">
-        <v>3.697299999999999</v>
+        <v>3.875599999999999</v>
       </c>
       <c r="F33">
-        <v>5.527299999999999</v>
+        <v>5.7056</v>
       </c>
       <c r="G33">
         <v>4.42</v>
@@ -3981,45 +3981,45 @@
         <v>2.278</v>
       </c>
       <c r="M33">
-        <v>0.29571055</v>
+        <v>0.30981408</v>
       </c>
       <c r="N33">
-        <v>1.98228945</v>
+        <v>1.96818592</v>
       </c>
       <c r="O33">
-        <v>0.39645789</v>
+        <v>0.393637184</v>
       </c>
       <c r="P33">
-        <v>1.58583156</v>
+        <v>1.574548736</v>
       </c>
       <c r="Q33">
-        <v>1.62783156</v>
+        <v>1.616548736</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.14033238909486</v>
+        <v>0.1415180455490787</v>
       </c>
       <c r="T33">
-        <v>1.593951887412252</v>
+        <v>1.613943758570063</v>
       </c>
       <c r="U33">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V33">
         <v>0.2</v>
       </c>
       <c r="W33">
-        <v>0.0428</v>
+        <v>0.04344000000000001</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y33">
-        <v>7.703478959408112</v>
+        <v>7.352796877404669</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1101330709733735</v>
+        <v>0.1099703934712937</v>
       </c>
       <c r="C34">
-        <v>13.12458878367366</v>
+        <v>12.98281985959539</v>
       </c>
       <c r="D34">
-        <v>14.41018878367366</v>
+        <v>14.44671985959539</v>
       </c>
       <c r="E34">
-        <v>3.875599999999999</v>
+        <v>4.0539</v>
       </c>
       <c r="F34">
-        <v>5.7056</v>
+        <v>5.8839</v>
       </c>
       <c r="G34">
         <v>4.42</v>
@@ -4063,28 +4063,28 @@
         <v>2.278</v>
       </c>
       <c r="M34">
-        <v>0.30981408</v>
+        <v>0.31949577</v>
       </c>
       <c r="N34">
-        <v>1.96818592</v>
+        <v>1.95850423</v>
       </c>
       <c r="O34">
-        <v>0.393637184</v>
+        <v>0.391700846</v>
       </c>
       <c r="P34">
-        <v>1.574548736</v>
+        <v>1.566803384</v>
       </c>
       <c r="Q34">
-        <v>1.616548736</v>
+        <v>1.608803384</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1415180455490787</v>
+        <v>0.1427390947332741</v>
       </c>
       <c r="T34">
-        <v>1.613943758570063</v>
+        <v>1.634532402001242</v>
       </c>
       <c r="U34">
         <v>0.0543</v>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>7.352796877404669</v>
+        <v>7.129984850816648</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1099703934712937</v>
+        <v>0.1098077159692138</v>
       </c>
       <c r="C35">
-        <v>12.98281985959539</v>
+        <v>12.84123662513561</v>
       </c>
       <c r="D35">
-        <v>14.44671985959539</v>
+        <v>14.48343662513561</v>
       </c>
       <c r="E35">
-        <v>4.0539</v>
+        <v>4.2322</v>
       </c>
       <c r="F35">
-        <v>5.8839</v>
+        <v>6.0622</v>
       </c>
       <c r="G35">
         <v>4.42</v>
@@ -4145,28 +4145,28 @@
         <v>2.278</v>
       </c>
       <c r="M35">
-        <v>0.31949577</v>
+        <v>0.32917746</v>
       </c>
       <c r="N35">
-        <v>1.95850423</v>
+        <v>1.94882254</v>
       </c>
       <c r="O35">
-        <v>0.391700846</v>
+        <v>0.3897645080000001</v>
       </c>
       <c r="P35">
-        <v>1.566803384</v>
+        <v>1.559058032</v>
       </c>
       <c r="Q35">
-        <v>1.608803384</v>
+        <v>1.601058032</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1427390947332741</v>
+        <v>0.1439971454078997</v>
       </c>
       <c r="T35">
-        <v>1.634532402001242</v>
+        <v>1.655744943718213</v>
       </c>
       <c r="U35">
         <v>0.0543</v>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>7.129984850816648</v>
+        <v>6.920279414027924</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1098077159692138</v>
+        <v>0.1096450384671339</v>
       </c>
       <c r="C36">
-        <v>12.84123662513561</v>
+        <v>12.69984049970876</v>
       </c>
       <c r="D36">
-        <v>14.48343662513561</v>
+        <v>14.52034049970876</v>
       </c>
       <c r="E36">
-        <v>4.2322</v>
+        <v>4.4105</v>
       </c>
       <c r="F36">
-        <v>6.0622</v>
+        <v>6.2405</v>
       </c>
       <c r="G36">
         <v>4.42</v>
@@ -4227,28 +4227,28 @@
         <v>2.278</v>
       </c>
       <c r="M36">
-        <v>0.32917746</v>
+        <v>0.33885915</v>
       </c>
       <c r="N36">
-        <v>1.94882254</v>
+        <v>1.93914085</v>
       </c>
       <c r="O36">
-        <v>0.3897645080000001</v>
+        <v>0.38782817</v>
       </c>
       <c r="P36">
-        <v>1.559058032</v>
+        <v>1.55131268</v>
       </c>
       <c r="Q36">
-        <v>1.601058032</v>
+        <v>1.59331268</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1439971454078997</v>
+        <v>0.1452939053340522</v>
       </c>
       <c r="T36">
-        <v>1.655744943718213</v>
+        <v>1.677610179026476</v>
       </c>
       <c r="U36">
         <v>0.0543</v>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>6.920279414027924</v>
+        <v>6.722557145055696</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1096450384671339</v>
+        <v>0.1094823609650541</v>
       </c>
       <c r="C37">
-        <v>12.69984049970876</v>
+        <v>12.55863291723294</v>
       </c>
       <c r="D37">
-        <v>14.52034049970876</v>
+        <v>14.55743291723294</v>
       </c>
       <c r="E37">
-        <v>4.4105</v>
+        <v>4.5888</v>
       </c>
       <c r="F37">
-        <v>6.2405</v>
+        <v>6.4188</v>
       </c>
       <c r="G37">
         <v>4.42</v>
@@ -4309,28 +4309,28 @@
         <v>2.278</v>
       </c>
       <c r="M37">
-        <v>0.33885915</v>
+        <v>0.34854084</v>
       </c>
       <c r="N37">
-        <v>1.93914085</v>
+        <v>1.92945916</v>
       </c>
       <c r="O37">
-        <v>0.38782817</v>
+        <v>0.385891832</v>
       </c>
       <c r="P37">
-        <v>1.55131268</v>
+        <v>1.543567328</v>
       </c>
       <c r="Q37">
-        <v>1.59331268</v>
+        <v>1.585567328</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1452939053340522</v>
+        <v>0.146631189007897</v>
       </c>
       <c r="T37">
-        <v>1.677610179026476</v>
+        <v>1.700158702938122</v>
       </c>
       <c r="U37">
         <v>0.0543</v>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>6.722557145055696</v>
+        <v>6.535819446581927</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1094823609650541</v>
+        <v>0.1093196834629742</v>
       </c>
       <c r="C38">
-        <v>12.55863291723295</v>
+        <v>12.41761532631565</v>
       </c>
       <c r="D38">
-        <v>14.55743291723294</v>
+        <v>14.59471532631565</v>
       </c>
       <c r="E38">
-        <v>4.588799999999999</v>
+        <v>4.767099999999999</v>
       </c>
       <c r="F38">
-        <v>6.418799999999999</v>
+        <v>6.597099999999999</v>
       </c>
       <c r="G38">
         <v>4.42</v>
@@ -4391,28 +4391,28 @@
         <v>2.278</v>
       </c>
       <c r="M38">
-        <v>0.34854084</v>
+        <v>0.35822253</v>
       </c>
       <c r="N38">
-        <v>1.92945916</v>
+        <v>1.91977747</v>
       </c>
       <c r="O38">
-        <v>0.385891832</v>
+        <v>0.3839554940000001</v>
       </c>
       <c r="P38">
-        <v>1.543567328</v>
+        <v>1.535821976</v>
       </c>
       <c r="Q38">
-        <v>1.585567328</v>
+        <v>1.577821976</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.146631189007897</v>
+        <v>0.1480109261317051</v>
       </c>
       <c r="T38">
-        <v>1.700158702938122</v>
+        <v>1.723423053005694</v>
       </c>
       <c r="U38">
         <v>0.0543</v>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>6.535819446581928</v>
+        <v>6.359175677755389</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1093196834629742</v>
+        <v>0.1091570059608944</v>
       </c>
       <c r="C39">
-        <v>12.41761532631565</v>
+        <v>12.27678919044233</v>
       </c>
       <c r="D39">
-        <v>14.59471532631565</v>
+        <v>14.63218919044233</v>
       </c>
       <c r="E39">
-        <v>4.767099999999999</v>
+        <v>4.945399999999999</v>
       </c>
       <c r="F39">
-        <v>6.597099999999999</v>
+        <v>6.775399999999999</v>
       </c>
       <c r="G39">
         <v>4.42</v>
@@ -4473,28 +4473,28 @@
         <v>2.278</v>
       </c>
       <c r="M39">
-        <v>0.35822253</v>
+        <v>0.3679042199999999</v>
       </c>
       <c r="N39">
-        <v>1.91977747</v>
+        <v>1.91009578</v>
       </c>
       <c r="O39">
-        <v>0.3839554940000001</v>
+        <v>0.382019156</v>
       </c>
       <c r="P39">
-        <v>1.535821976</v>
+        <v>1.528076624</v>
       </c>
       <c r="Q39">
-        <v>1.577821976</v>
+        <v>1.570076624</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1480109261317051</v>
+        <v>0.1494351709046683</v>
       </c>
       <c r="T39">
-        <v>1.723423053005694</v>
+        <v>1.74743786597867</v>
       </c>
       <c r="U39">
         <v>0.0543</v>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>6.359175677755389</v>
+        <v>6.191828949393406</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1091570059608944</v>
+        <v>0.1093063284588145</v>
       </c>
       <c r="C40">
-        <v>12.27678919044233</v>
+        <v>12.06408450837393</v>
       </c>
       <c r="D40">
-        <v>14.63218919044233</v>
+        <v>14.59778450837393</v>
       </c>
       <c r="E40">
-        <v>4.945399999999999</v>
+        <v>5.123699999999999</v>
       </c>
       <c r="F40">
-        <v>6.775399999999999</v>
+        <v>6.9537</v>
       </c>
       <c r="G40">
         <v>4.42</v>
@@ -4555,45 +4555,45 @@
         <v>2.278</v>
       </c>
       <c r="M40">
-        <v>0.3679042199999999</v>
+        <v>0.38453961</v>
       </c>
       <c r="N40">
-        <v>1.91009578</v>
+        <v>1.89346039</v>
       </c>
       <c r="O40">
-        <v>0.382019156</v>
+        <v>0.378692078</v>
       </c>
       <c r="P40">
-        <v>1.528076624</v>
+        <v>1.514768312</v>
       </c>
       <c r="Q40">
-        <v>1.570076624</v>
+        <v>1.556768312</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1494351709046683</v>
+        <v>0.1509061122275648</v>
       </c>
       <c r="T40">
-        <v>1.74743786597867</v>
+        <v>1.772240049868794</v>
       </c>
       <c r="U40">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V40">
         <v>0.2</v>
       </c>
       <c r="W40">
-        <v>0.04344000000000001</v>
+        <v>0.04424</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y40">
-        <v>6.191828949393406</v>
+        <v>5.923967104455118</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1093063284588145</v>
+        <v>0.1091516509567347</v>
       </c>
       <c r="C41">
-        <v>12.06408450837393</v>
+        <v>11.92142602378127</v>
       </c>
       <c r="D41">
-        <v>14.59778450837393</v>
+        <v>14.63342602378127</v>
       </c>
       <c r="E41">
-        <v>5.123699999999999</v>
+        <v>5.302</v>
       </c>
       <c r="F41">
-        <v>6.9537</v>
+        <v>7.132</v>
       </c>
       <c r="G41">
         <v>4.42</v>
@@ -4637,28 +4637,28 @@
         <v>2.278</v>
       </c>
       <c r="M41">
-        <v>0.38453961</v>
+        <v>0.3943996</v>
       </c>
       <c r="N41">
-        <v>1.89346039</v>
+        <v>1.8836004</v>
       </c>
       <c r="O41">
-        <v>0.378692078</v>
+        <v>0.37672008</v>
       </c>
       <c r="P41">
-        <v>1.514768312</v>
+        <v>1.50688032</v>
       </c>
       <c r="Q41">
-        <v>1.556768312</v>
+        <v>1.54888032</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1509061122275648</v>
+        <v>0.1524260849278911</v>
       </c>
       <c r="T41">
-        <v>1.772240049868794</v>
+        <v>1.797868973221922</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.923967104455118</v>
+        <v>5.775867926843739</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1091516509567347</v>
+        <v>0.1089969734546548</v>
       </c>
       <c r="C42">
-        <v>11.92142602378127</v>
+        <v>11.77894200768837</v>
       </c>
       <c r="D42">
-        <v>14.63342602378127</v>
+        <v>14.66924200768837</v>
       </c>
       <c r="E42">
-        <v>5.302</v>
+        <v>5.4803</v>
       </c>
       <c r="F42">
-        <v>7.132</v>
+        <v>7.3103</v>
       </c>
       <c r="G42">
         <v>4.42</v>
@@ -4719,28 +4719,28 @@
         <v>2.278</v>
       </c>
       <c r="M42">
-        <v>0.3943996</v>
+        <v>0.40425959</v>
       </c>
       <c r="N42">
-        <v>1.8836004</v>
+        <v>1.87374041</v>
       </c>
       <c r="O42">
-        <v>0.37672008</v>
+        <v>0.374748082</v>
       </c>
       <c r="P42">
-        <v>1.50688032</v>
+        <v>1.498992328</v>
       </c>
       <c r="Q42">
-        <v>1.54888032</v>
+        <v>1.540992328</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1524260849278911</v>
+        <v>0.1539975821265335</v>
       </c>
       <c r="T42">
-        <v>1.797868973221922</v>
+        <v>1.824366673637868</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.775867926843739</v>
+        <v>5.634993099359745</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1089969734546548</v>
+        <v>0.1088422959525749</v>
       </c>
       <c r="C43">
-        <v>11.77894200768837</v>
+        <v>11.6366337442974</v>
       </c>
       <c r="D43">
-        <v>14.66924200768837</v>
+        <v>14.7052337442974</v>
       </c>
       <c r="E43">
-        <v>5.4803</v>
+        <v>5.6586</v>
       </c>
       <c r="F43">
-        <v>7.3103</v>
+        <v>7.4886</v>
       </c>
       <c r="G43">
         <v>4.42</v>
@@ -4801,28 +4801,28 @@
         <v>2.278</v>
       </c>
       <c r="M43">
-        <v>0.40425959</v>
+        <v>0.41411958</v>
       </c>
       <c r="N43">
-        <v>1.87374041</v>
+        <v>1.86388042</v>
       </c>
       <c r="O43">
-        <v>0.374748082</v>
+        <v>0.3727760840000001</v>
       </c>
       <c r="P43">
-        <v>1.498992328</v>
+        <v>1.491104336</v>
       </c>
       <c r="Q43">
-        <v>1.540992328</v>
+        <v>1.533104336</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1539975821265335</v>
+        <v>0.1556232688837499</v>
       </c>
       <c r="T43">
-        <v>1.824366673637868</v>
+        <v>1.85177808786126</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>5.634993099359745</v>
+        <v>5.500826596994037</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1088422959525749</v>
+        <v>0.1086876184504951</v>
       </c>
       <c r="C44">
-        <v>11.6366337442974</v>
+        <v>11.49450253044501</v>
       </c>
       <c r="D44">
-        <v>14.7052337442974</v>
+        <v>14.74140253044501</v>
       </c>
       <c r="E44">
-        <v>5.658599999999999</v>
+        <v>5.836899999999999</v>
       </c>
       <c r="F44">
-        <v>7.488599999999999</v>
+        <v>7.666899999999999</v>
       </c>
       <c r="G44">
         <v>4.42</v>
@@ -4883,28 +4883,28 @@
         <v>2.278</v>
       </c>
       <c r="M44">
-        <v>0.41411958</v>
+        <v>0.42397957</v>
       </c>
       <c r="N44">
-        <v>1.86388042</v>
+        <v>1.85402043</v>
       </c>
       <c r="O44">
-        <v>0.3727760840000001</v>
+        <v>0.370804086</v>
       </c>
       <c r="P44">
-        <v>1.491104336</v>
+        <v>1.483216344</v>
       </c>
       <c r="Q44">
-        <v>1.533104336</v>
+        <v>1.525216344</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1556232688837499</v>
+        <v>0.1573059972815703</v>
       </c>
       <c r="T44">
-        <v>1.85177808786126</v>
+        <v>1.880151306092491</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>5.500826596994037</v>
+        <v>5.372900397063944</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1086876184504951</v>
+        <v>0.1085329409484152</v>
       </c>
       <c r="C45">
-        <v>11.49450253044501</v>
+        <v>11.35254967575799</v>
       </c>
       <c r="D45">
-        <v>14.74140253044501</v>
+        <v>14.77774967575799</v>
       </c>
       <c r="E45">
-        <v>5.836899999999999</v>
+        <v>6.015199999999999</v>
       </c>
       <c r="F45">
-        <v>7.666899999999999</v>
+        <v>7.845199999999999</v>
       </c>
       <c r="G45">
         <v>4.42</v>
@@ -4965,28 +4965,28 @@
         <v>2.278</v>
       </c>
       <c r="M45">
-        <v>0.42397957</v>
+        <v>0.43383956</v>
       </c>
       <c r="N45">
-        <v>1.85402043</v>
+        <v>1.84416044</v>
       </c>
       <c r="O45">
-        <v>0.370804086</v>
+        <v>0.368832088</v>
       </c>
       <c r="P45">
-        <v>1.483216344</v>
+        <v>1.475328352</v>
       </c>
       <c r="Q45">
-        <v>1.525216344</v>
+        <v>1.517328352</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1573059972815703</v>
+        <v>0.15904882312217</v>
       </c>
       <c r="T45">
-        <v>1.880151306092491</v>
+        <v>1.909537853546265</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>5.372900397063944</v>
+        <v>5.250789024403399</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1085329409484152</v>
+        <v>0.1083782634463354</v>
       </c>
       <c r="C46">
-        <v>11.35254967575799</v>
+        <v>11.21077650281141</v>
       </c>
       <c r="D46">
-        <v>14.77774967575799</v>
+        <v>14.81427650281141</v>
       </c>
       <c r="E46">
-        <v>6.015199999999999</v>
+        <v>6.1935</v>
       </c>
       <c r="F46">
-        <v>7.845199999999999</v>
+        <v>8.0235</v>
       </c>
       <c r="G46">
         <v>4.42</v>
@@ -5047,28 +5047,28 @@
         <v>2.278</v>
       </c>
       <c r="M46">
-        <v>0.43383956</v>
+        <v>0.4436995500000001</v>
       </c>
       <c r="N46">
-        <v>1.84416044</v>
+        <v>1.83430045</v>
       </c>
       <c r="O46">
-        <v>0.368832088</v>
+        <v>0.36686009</v>
       </c>
       <c r="P46">
-        <v>1.475328352</v>
+        <v>1.46744036</v>
       </c>
       <c r="Q46">
-        <v>1.517328352</v>
+        <v>1.50944036</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.15904882312217</v>
+        <v>0.1608550244478825</v>
       </c>
       <c r="T46">
-        <v>1.909537853546265</v>
+        <v>1.939993002725631</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>5.250789024403399</v>
+        <v>5.134104823861101</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1083782634463354</v>
+        <v>0.1082235859442555</v>
       </c>
       <c r="C47">
-        <v>11.21077650281141</v>
+        <v>11.069184347289</v>
       </c>
       <c r="D47">
-        <v>14.81427650281141</v>
+        <v>14.850984347289</v>
       </c>
       <c r="E47">
-        <v>6.1935</v>
+        <v>6.3718</v>
       </c>
       <c r="F47">
-        <v>8.0235</v>
+        <v>8.2018</v>
       </c>
       <c r="G47">
         <v>4.42</v>
@@ -5129,28 +5129,28 @@
         <v>2.278</v>
       </c>
       <c r="M47">
-        <v>0.4436995500000001</v>
+        <v>0.45355954</v>
       </c>
       <c r="N47">
-        <v>1.83430045</v>
+        <v>1.82444046</v>
       </c>
       <c r="O47">
-        <v>0.36686009</v>
+        <v>0.364888092</v>
       </c>
       <c r="P47">
-        <v>1.46744036</v>
+        <v>1.459552368</v>
       </c>
       <c r="Q47">
-        <v>1.50944036</v>
+        <v>1.501552368</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1608550244478825</v>
+        <v>0.1627281221189917</v>
       </c>
       <c r="T47">
-        <v>1.939993002725631</v>
+        <v>1.971576120393123</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>5.134104823861101</v>
+        <v>5.022493849429338</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1082235859442555</v>
+        <v>0.1080689084421756</v>
       </c>
       <c r="C48">
-        <v>11.069184347289</v>
+        <v>10.92777455814598</v>
       </c>
       <c r="D48">
-        <v>14.850984347289</v>
+        <v>14.88787455814598</v>
       </c>
       <c r="E48">
-        <v>6.3718</v>
+        <v>6.5501</v>
       </c>
       <c r="F48">
-        <v>8.2018</v>
+        <v>8.380100000000001</v>
       </c>
       <c r="G48">
         <v>4.42</v>
@@ -5211,28 +5211,28 @@
         <v>2.278</v>
       </c>
       <c r="M48">
-        <v>0.45355954</v>
+        <v>0.46341953</v>
       </c>
       <c r="N48">
-        <v>1.82444046</v>
+        <v>1.81458047</v>
       </c>
       <c r="O48">
-        <v>0.364888092</v>
+        <v>0.362916094</v>
       </c>
       <c r="P48">
-        <v>1.459552368</v>
+        <v>1.451664376</v>
       </c>
       <c r="Q48">
-        <v>1.501552368</v>
+        <v>1.493664376</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1627281221189917</v>
+        <v>0.1646719027210861</v>
       </c>
       <c r="T48">
-        <v>1.971576120393123</v>
+        <v>2.004351053821651</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>5.022493849429338</v>
+        <v>4.915632278164884</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1080689084421756</v>
+        <v>0.1079142309400958</v>
       </c>
       <c r="C49">
-        <v>10.92777455814598</v>
+        <v>10.78654849777429</v>
       </c>
       <c r="D49">
-        <v>14.88787455814598</v>
+        <v>14.92494849777429</v>
       </c>
       <c r="E49">
-        <v>6.5501</v>
+        <v>6.728400000000001</v>
       </c>
       <c r="F49">
-        <v>8.380100000000001</v>
+        <v>8.558400000000001</v>
       </c>
       <c r="G49">
         <v>4.42</v>
@@ -5293,28 +5293,28 @@
         <v>2.278</v>
       </c>
       <c r="M49">
-        <v>0.46341953</v>
+        <v>0.4732795200000001</v>
       </c>
       <c r="N49">
-        <v>1.81458047</v>
+        <v>1.80472048</v>
       </c>
       <c r="O49">
-        <v>0.362916094</v>
+        <v>0.360944096</v>
       </c>
       <c r="P49">
-        <v>1.451664376</v>
+        <v>1.443776384</v>
       </c>
       <c r="Q49">
-        <v>1.493664376</v>
+        <v>1.485776384</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1646719027210861</v>
+        <v>0.1666904441155688</v>
       </c>
       <c r="T49">
-        <v>2.004351053821651</v>
+        <v>2.038386561612815</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>4.915632278164884</v>
+        <v>4.813223272369782</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1079142309400958</v>
+        <v>0.1077595534380159</v>
       </c>
       <c r="C50">
-        <v>10.7865484977743</v>
+        <v>10.64550754217034</v>
       </c>
       <c r="D50">
-        <v>14.9249484977743</v>
+        <v>14.96220754217034</v>
       </c>
       <c r="E50">
-        <v>6.728399999999999</v>
+        <v>6.906699999999999</v>
       </c>
       <c r="F50">
-        <v>8.558399999999999</v>
+        <v>8.736699999999999</v>
       </c>
       <c r="G50">
         <v>4.42</v>
@@ -5375,28 +5375,28 @@
         <v>2.278</v>
       </c>
       <c r="M50">
-        <v>0.47327952</v>
+        <v>0.4831395099999999</v>
       </c>
       <c r="N50">
-        <v>1.80472048</v>
+        <v>1.79486049</v>
       </c>
       <c r="O50">
-        <v>0.360944096</v>
+        <v>0.358972098</v>
       </c>
       <c r="P50">
-        <v>1.443776384</v>
+        <v>1.435888392</v>
       </c>
       <c r="Q50">
-        <v>1.485776384</v>
+        <v>1.477888392</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1666904441155688</v>
+        <v>0.1687881439961097</v>
       </c>
       <c r="T50">
-        <v>2.038386561612815</v>
+        <v>2.073756795199711</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>4.813223272369783</v>
+        <v>4.714994225994889</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1077595534380159</v>
+        <v>0.1076048759359361</v>
       </c>
       <c r="C51">
-        <v>10.64550754217034</v>
+        <v>10.5046530811052</v>
       </c>
       <c r="D51">
-        <v>14.96220754217034</v>
+        <v>14.9996530811052</v>
       </c>
       <c r="E51">
-        <v>6.906699999999999</v>
+        <v>7.084999999999999</v>
       </c>
       <c r="F51">
-        <v>8.736699999999999</v>
+        <v>8.914999999999999</v>
       </c>
       <c r="G51">
         <v>4.42</v>
@@ -5457,28 +5457,28 @@
         <v>2.278</v>
       </c>
       <c r="M51">
-        <v>0.4831395099999999</v>
+        <v>0.4929995</v>
       </c>
       <c r="N51">
-        <v>1.79486049</v>
+        <v>1.7850005</v>
       </c>
       <c r="O51">
-        <v>0.358972098</v>
+        <v>0.3570001</v>
       </c>
       <c r="P51">
-        <v>1.435888392</v>
+        <v>1.4280004</v>
       </c>
       <c r="Q51">
-        <v>1.477888392</v>
+        <v>1.4700004</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1687881439961097</v>
+        <v>0.1709697518718721</v>
       </c>
       <c r="T51">
-        <v>2.073756795199711</v>
+        <v>2.110541838130083</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>4.714994225994889</v>
+        <v>4.620694341474992</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1076048759359361</v>
+        <v>0.1074501984338562</v>
       </c>
       <c r="C52">
-        <v>10.5046530811052</v>
+        <v>10.36398651829744</v>
       </c>
       <c r="D52">
-        <v>14.9996530811052</v>
+        <v>15.03728651829745</v>
       </c>
       <c r="E52">
-        <v>7.084999999999999</v>
+        <v>7.263299999999999</v>
       </c>
       <c r="F52">
-        <v>8.914999999999999</v>
+        <v>9.093299999999999</v>
       </c>
       <c r="G52">
         <v>4.42</v>
@@ -5539,28 +5539,28 @@
         <v>2.278</v>
       </c>
       <c r="M52">
-        <v>0.4929995</v>
+        <v>0.50285949</v>
       </c>
       <c r="N52">
-        <v>1.7850005</v>
+        <v>1.77514051</v>
       </c>
       <c r="O52">
-        <v>0.3570001</v>
+        <v>0.355028102</v>
       </c>
       <c r="P52">
-        <v>1.4280004</v>
+        <v>1.420112408</v>
       </c>
       <c r="Q52">
-        <v>1.4700004</v>
+        <v>1.462112408</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1709697518718721</v>
+        <v>0.1732404049670535</v>
       </c>
       <c r="T52">
-        <v>2.110541838130083</v>
+        <v>2.148828311384143</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>4.620694341474992</v>
+        <v>4.530092491642149</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1074501984338562</v>
+        <v>0.1083355209317763</v>
       </c>
       <c r="C53">
-        <v>10.36398651829744</v>
+        <v>9.972801939038185</v>
       </c>
       <c r="D53">
-        <v>15.03728651829745</v>
+        <v>14.82440193903819</v>
       </c>
       <c r="E53">
-        <v>7.263299999999999</v>
+        <v>7.441599999999999</v>
       </c>
       <c r="F53">
-        <v>9.093299999999999</v>
+        <v>9.271599999999999</v>
       </c>
       <c r="G53">
         <v>4.42</v>
@@ -5621,45 +5621,45 @@
         <v>2.278</v>
       </c>
       <c r="M53">
-        <v>0.50285949</v>
+        <v>0.53589848</v>
       </c>
       <c r="N53">
-        <v>1.77514051</v>
+        <v>1.74210152</v>
       </c>
       <c r="O53">
-        <v>0.355028102</v>
+        <v>0.348420304</v>
       </c>
       <c r="P53">
-        <v>1.420112408</v>
+        <v>1.393681216</v>
       </c>
       <c r="Q53">
-        <v>1.462112408</v>
+        <v>1.435681216</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1732404049670535</v>
+        <v>0.1756056686078674</v>
       </c>
       <c r="T53">
-        <v>2.148828311384143</v>
+        <v>2.188710054357123</v>
       </c>
       <c r="U53">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V53">
         <v>0.2</v>
       </c>
       <c r="W53">
-        <v>0.04424</v>
+        <v>0.04624</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y53">
-        <v>4.530092491642149</v>
+        <v>4.250805115177785</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1083355209317763</v>
+        <v>0.1082008434296965</v>
       </c>
       <c r="C54">
-        <v>9.972801939038185</v>
+        <v>9.826496913997566</v>
       </c>
       <c r="D54">
-        <v>14.82440193903819</v>
+        <v>14.85639691399757</v>
       </c>
       <c r="E54">
-        <v>7.441599999999999</v>
+        <v>7.619899999999999</v>
       </c>
       <c r="F54">
-        <v>9.271599999999999</v>
+        <v>9.4499</v>
       </c>
       <c r="G54">
         <v>4.42</v>
@@ -5703,28 +5703,28 @@
         <v>2.278</v>
       </c>
       <c r="M54">
-        <v>0.53589848</v>
+        <v>0.54620422</v>
       </c>
       <c r="N54">
-        <v>1.74210152</v>
+        <v>1.73179578</v>
       </c>
       <c r="O54">
-        <v>0.348420304</v>
+        <v>0.3463591560000001</v>
       </c>
       <c r="P54">
-        <v>1.393681216</v>
+        <v>1.385436624</v>
       </c>
       <c r="Q54">
-        <v>1.435681216</v>
+        <v>1.427436624</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1756056686078674</v>
+        <v>0.1780715817653117</v>
       </c>
       <c r="T54">
-        <v>2.188710054357123</v>
+        <v>2.230288892775761</v>
       </c>
       <c r="U54">
         <v>0.0578</v>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>4.250805115177785</v>
+        <v>4.170601245080091</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1082008434296965</v>
+        <v>0.1080661659276167</v>
       </c>
       <c r="C55">
-        <v>9.826496913997566</v>
+        <v>9.680330294887113</v>
       </c>
       <c r="D55">
-        <v>14.85639691399757</v>
+        <v>14.88853029488711</v>
       </c>
       <c r="E55">
-        <v>7.619899999999999</v>
+        <v>7.7982</v>
       </c>
       <c r="F55">
-        <v>9.4499</v>
+        <v>9.6282</v>
       </c>
       <c r="G55">
         <v>4.42</v>
@@ -5785,28 +5785,28 @@
         <v>2.278</v>
       </c>
       <c r="M55">
-        <v>0.54620422</v>
+        <v>0.55650996</v>
       </c>
       <c r="N55">
-        <v>1.73179578</v>
+        <v>1.72149004</v>
       </c>
       <c r="O55">
-        <v>0.3463591560000001</v>
+        <v>0.344298008</v>
       </c>
       <c r="P55">
-        <v>1.385436624</v>
+        <v>1.377192032</v>
       </c>
       <c r="Q55">
-        <v>1.427436624</v>
+        <v>1.419192032</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1780715817653117</v>
+        <v>0.1806447085382971</v>
       </c>
       <c r="T55">
-        <v>2.230288892775761</v>
+        <v>2.273675506777819</v>
       </c>
       <c r="U55">
         <v>0.0578</v>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>4.170601245080091</v>
+        <v>4.093367888689719</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1080661659276167</v>
+        <v>0.1079314884255368</v>
       </c>
       <c r="C56">
-        <v>9.680330294887113</v>
+        <v>9.534302981741526</v>
       </c>
       <c r="D56">
-        <v>14.88853029488711</v>
+        <v>14.92080298174152</v>
       </c>
       <c r="E56">
-        <v>7.7982</v>
+        <v>7.9765</v>
       </c>
       <c r="F56">
-        <v>9.6282</v>
+        <v>9.8065</v>
       </c>
       <c r="G56">
         <v>4.42</v>
@@ -5867,28 +5867,28 @@
         <v>2.278</v>
       </c>
       <c r="M56">
-        <v>0.55650996</v>
+        <v>0.5668157</v>
       </c>
       <c r="N56">
-        <v>1.72149004</v>
+        <v>1.7111843</v>
       </c>
       <c r="O56">
-        <v>0.344298008</v>
+        <v>0.34223686</v>
       </c>
       <c r="P56">
-        <v>1.377192032</v>
+        <v>1.36894744</v>
       </c>
       <c r="Q56">
-        <v>1.419192032</v>
+        <v>1.41094744</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1806447085382971</v>
+        <v>0.1833321965011929</v>
       </c>
       <c r="T56">
-        <v>2.273675506777819</v>
+        <v>2.318990414735523</v>
       </c>
       <c r="U56">
         <v>0.0578</v>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>4.093367888689719</v>
+        <v>4.01894301798627</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1079314884255368</v>
+        <v>0.1093648109234569</v>
       </c>
       <c r="C57">
-        <v>9.534302981741526</v>
+        <v>9.019553894737761</v>
       </c>
       <c r="D57">
-        <v>14.92080298174152</v>
+        <v>14.58435389473776</v>
       </c>
       <c r="E57">
-        <v>7.9765</v>
+        <v>8.1548</v>
       </c>
       <c r="F57">
-        <v>9.8065</v>
+        <v>9.9848</v>
       </c>
       <c r="G57">
         <v>4.42</v>
@@ -5949,45 +5949,45 @@
         <v>2.278</v>
       </c>
       <c r="M57">
-        <v>0.5668157</v>
+        <v>0.61206824</v>
       </c>
       <c r="N57">
-        <v>1.7111843</v>
+        <v>1.66593176</v>
       </c>
       <c r="O57">
-        <v>0.34223686</v>
+        <v>0.333186352</v>
       </c>
       <c r="P57">
-        <v>1.36894744</v>
+        <v>1.332745408</v>
       </c>
       <c r="Q57">
-        <v>1.41094744</v>
+        <v>1.374745408</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1833321965011929</v>
+        <v>0.1861418430078567</v>
       </c>
       <c r="T57">
-        <v>2.318990414735523</v>
+        <v>2.36636509123676</v>
       </c>
       <c r="U57">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V57">
         <v>0.2</v>
       </c>
       <c r="W57">
-        <v>0.04624</v>
+        <v>0.04904</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y57">
-        <v>4.01894301798627</v>
+        <v>3.72180722855347</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1093648109234569</v>
+        <v>0.1092581334213771</v>
       </c>
       <c r="C58">
-        <v>9.019553894737761</v>
+        <v>8.86577120022811</v>
       </c>
       <c r="D58">
-        <v>14.58435389473776</v>
+        <v>14.60887120022811</v>
       </c>
       <c r="E58">
-        <v>8.1548</v>
+        <v>8.3331</v>
       </c>
       <c r="F58">
-        <v>9.9848</v>
+        <v>10.1631</v>
       </c>
       <c r="G58">
         <v>4.42</v>
@@ -6031,28 +6031,28 @@
         <v>2.278</v>
       </c>
       <c r="M58">
-        <v>0.61206824</v>
+        <v>0.62299803</v>
       </c>
       <c r="N58">
-        <v>1.66593176</v>
+        <v>1.65500197</v>
       </c>
       <c r="O58">
-        <v>0.333186352</v>
+        <v>0.331000394</v>
       </c>
       <c r="P58">
-        <v>1.332745408</v>
+        <v>1.324001576</v>
       </c>
       <c r="Q58">
-        <v>1.374745408</v>
+        <v>1.366001576</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1861418430078567</v>
+        <v>0.1890821707473886</v>
       </c>
       <c r="T58">
-        <v>2.36636509123676</v>
+        <v>2.415943241063635</v>
       </c>
       <c r="U58">
         <v>0.0613</v>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.72180722855347</v>
+        <v>3.656512364894637</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1092581334213771</v>
+        <v>0.1091514559192972</v>
       </c>
       <c r="C59">
-        <v>8.86577120022811</v>
+        <v>8.712071075088637</v>
       </c>
       <c r="D59">
-        <v>14.60887120022811</v>
+        <v>14.63347107508864</v>
       </c>
       <c r="E59">
-        <v>8.3331</v>
+        <v>8.5114</v>
       </c>
       <c r="F59">
-        <v>10.1631</v>
+        <v>10.3414</v>
       </c>
       <c r="G59">
         <v>4.42</v>
@@ -6113,28 +6113,28 @@
         <v>2.278</v>
       </c>
       <c r="M59">
-        <v>0.62299803</v>
+        <v>0.63392782</v>
       </c>
       <c r="N59">
-        <v>1.65500197</v>
+        <v>1.64407218</v>
       </c>
       <c r="O59">
-        <v>0.331000394</v>
+        <v>0.328814436</v>
       </c>
       <c r="P59">
-        <v>1.324001576</v>
+        <v>1.315257744</v>
       </c>
       <c r="Q59">
-        <v>1.366001576</v>
+        <v>1.357257744</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1890821707473886</v>
+        <v>0.1921625140935648</v>
       </c>
       <c r="T59">
-        <v>2.415943241063635</v>
+        <v>2.467882255167981</v>
       </c>
       <c r="U59">
         <v>0.0613</v>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.656512364894637</v>
+        <v>3.593469048258522</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1091514559192972</v>
+        <v>0.1090447784172174</v>
       </c>
       <c r="C60">
-        <v>8.712071075088639</v>
+        <v>8.558453937138532</v>
       </c>
       <c r="D60">
-        <v>14.63347107508864</v>
+        <v>14.65815393713853</v>
       </c>
       <c r="E60">
-        <v>8.511399999999998</v>
+        <v>8.689699999999998</v>
       </c>
       <c r="F60">
-        <v>10.3414</v>
+        <v>10.5197</v>
       </c>
       <c r="G60">
         <v>4.42</v>
@@ -6195,28 +6195,28 @@
         <v>2.278</v>
       </c>
       <c r="M60">
-        <v>0.6339278199999999</v>
+        <v>0.6448576099999999</v>
       </c>
       <c r="N60">
-        <v>1.64407218</v>
+        <v>1.63314239</v>
       </c>
       <c r="O60">
-        <v>0.328814436</v>
+        <v>0.3266284780000001</v>
       </c>
       <c r="P60">
-        <v>1.315257744</v>
+        <v>1.306513912</v>
       </c>
       <c r="Q60">
-        <v>1.357257744</v>
+        <v>1.348513912</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1921625140935647</v>
+        <v>0.195393118090774</v>
       </c>
       <c r="T60">
-        <v>2.46788225516798</v>
+        <v>2.52235487971644</v>
       </c>
       <c r="U60">
         <v>0.0613</v>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>3.593469048258523</v>
+        <v>3.532562793203294</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1090447784172174</v>
+        <v>0.1102821009151375</v>
       </c>
       <c r="C61">
-        <v>8.558453937138532</v>
+        <v>8.098884198916638</v>
       </c>
       <c r="D61">
-        <v>14.65815393713853</v>
+        <v>14.37688419891663</v>
       </c>
       <c r="E61">
-        <v>8.689699999999998</v>
+        <v>8.867999999999999</v>
       </c>
       <c r="F61">
-        <v>10.5197</v>
+        <v>10.698</v>
       </c>
       <c r="G61">
         <v>4.42</v>
@@ -6277,45 +6277,45 @@
         <v>2.278</v>
       </c>
       <c r="M61">
-        <v>0.6448576099999999</v>
+        <v>0.6857418</v>
       </c>
       <c r="N61">
-        <v>1.63314239</v>
+        <v>1.5922582</v>
       </c>
       <c r="O61">
-        <v>0.3266284780000001</v>
+        <v>0.31845164</v>
       </c>
       <c r="P61">
-        <v>1.306513912</v>
+        <v>1.27380656</v>
       </c>
       <c r="Q61">
-        <v>1.348513912</v>
+        <v>1.31580656</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.195393118090774</v>
+        <v>0.1987852522878437</v>
       </c>
       <c r="T61">
-        <v>2.52235487971644</v>
+        <v>2.579551135492324</v>
       </c>
       <c r="U61">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V61">
         <v>0.2</v>
       </c>
       <c r="W61">
-        <v>0.04904</v>
+        <v>0.05128000000000001</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y61">
-        <v>3.532562793203294</v>
+        <v>3.321950040087975</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1102821009151375</v>
+        <v>0.1101978234130576</v>
       </c>
       <c r="C62">
-        <v>8.098884198916638</v>
+        <v>7.939399243024647</v>
       </c>
       <c r="D62">
-        <v>14.37688419891663</v>
+        <v>14.39569924302465</v>
       </c>
       <c r="E62">
-        <v>8.867999999999999</v>
+        <v>9.046299999999999</v>
       </c>
       <c r="F62">
-        <v>10.698</v>
+        <v>10.8763</v>
       </c>
       <c r="G62">
         <v>4.42</v>
@@ -6359,28 +6359,28 @@
         <v>2.278</v>
       </c>
       <c r="M62">
-        <v>0.6857418</v>
+        <v>0.69717083</v>
       </c>
       <c r="N62">
-        <v>1.5922582</v>
+        <v>1.58082917</v>
       </c>
       <c r="O62">
-        <v>0.31845164</v>
+        <v>0.316165834</v>
       </c>
       <c r="P62">
-        <v>1.27380656</v>
+        <v>1.264663336</v>
       </c>
       <c r="Q62">
-        <v>1.31580656</v>
+        <v>1.306663336</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1987852522878437</v>
+        <v>0.2023513420847631</v>
       </c>
       <c r="T62">
-        <v>2.579551135492324</v>
+        <v>2.639680532590046</v>
       </c>
       <c r="U62">
         <v>0.0641</v>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>3.321950040087975</v>
+        <v>3.267491842709483</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1101978234130576</v>
+        <v>0.1101135459109778</v>
       </c>
       <c r="C63">
-        <v>7.939399243024647</v>
+        <v>7.779963598203791</v>
       </c>
       <c r="D63">
-        <v>14.39569924302465</v>
+        <v>14.41456359820379</v>
       </c>
       <c r="E63">
-        <v>9.046299999999999</v>
+        <v>9.224599999999999</v>
       </c>
       <c r="F63">
-        <v>10.8763</v>
+        <v>11.0546</v>
       </c>
       <c r="G63">
         <v>4.42</v>
@@ -6441,28 +6441,28 @@
         <v>2.278</v>
       </c>
       <c r="M63">
-        <v>0.69717083</v>
+        <v>0.70859986</v>
       </c>
       <c r="N63">
-        <v>1.58082917</v>
+        <v>1.56940014</v>
       </c>
       <c r="O63">
-        <v>0.316165834</v>
+        <v>0.313880028</v>
       </c>
       <c r="P63">
-        <v>1.264663336</v>
+        <v>1.255520112</v>
       </c>
       <c r="Q63">
-        <v>1.306663336</v>
+        <v>1.297520112</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2023513420847631</v>
+        <v>0.2061051208183625</v>
       </c>
       <c r="T63">
-        <v>2.639680532590046</v>
+        <v>2.702974634798176</v>
       </c>
       <c r="U63">
         <v>0.0641</v>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>3.267491842709483</v>
+        <v>3.21479036137546</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1101135459109778</v>
+        <v>0.1100292684088979</v>
       </c>
       <c r="C64">
-        <v>7.779963598203791</v>
+        <v>7.620577458562495</v>
       </c>
       <c r="D64">
-        <v>14.41456359820379</v>
+        <v>14.43347745856249</v>
       </c>
       <c r="E64">
-        <v>9.224599999999999</v>
+        <v>9.402899999999999</v>
       </c>
       <c r="F64">
-        <v>11.0546</v>
+        <v>11.2329</v>
       </c>
       <c r="G64">
         <v>4.42</v>
@@ -6523,28 +6523,28 @@
         <v>2.278</v>
       </c>
       <c r="M64">
-        <v>0.70859986</v>
+        <v>0.72002889</v>
       </c>
       <c r="N64">
-        <v>1.56940014</v>
+        <v>1.55797111</v>
       </c>
       <c r="O64">
-        <v>0.313880028</v>
+        <v>0.311594222</v>
       </c>
       <c r="P64">
-        <v>1.255520112</v>
+        <v>1.246376888</v>
       </c>
       <c r="Q64">
-        <v>1.297520112</v>
+        <v>1.288376888</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2061051208183625</v>
+        <v>0.2100618065105349</v>
       </c>
       <c r="T64">
-        <v>2.702974634798176</v>
+        <v>2.769690039828367</v>
       </c>
       <c r="U64">
         <v>0.0641</v>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>3.21479036137546</v>
+        <v>3.163761942940928</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1100292684088979</v>
+        <v>0.1099449909068181</v>
       </c>
       <c r="C65">
-        <v>7.620577458562495</v>
+        <v>7.461241019229307</v>
       </c>
       <c r="D65">
-        <v>14.43347745856249</v>
+        <v>14.4524410192293</v>
       </c>
       <c r="E65">
-        <v>9.402899999999999</v>
+        <v>9.581199999999999</v>
       </c>
       <c r="F65">
-        <v>11.2329</v>
+        <v>11.4112</v>
       </c>
       <c r="G65">
         <v>4.42</v>
@@ -6605,28 +6605,28 @@
         <v>2.278</v>
       </c>
       <c r="M65">
-        <v>0.72002889</v>
+        <v>0.73145792</v>
       </c>
       <c r="N65">
-        <v>1.55797111</v>
+        <v>1.54654208</v>
       </c>
       <c r="O65">
-        <v>0.311594222</v>
+        <v>0.309308416</v>
       </c>
       <c r="P65">
-        <v>1.246376888</v>
+        <v>1.237233664</v>
       </c>
       <c r="Q65">
-        <v>1.288376888</v>
+        <v>1.279233664</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2100618065105349</v>
+        <v>0.2142383080744946</v>
       </c>
       <c r="T65">
-        <v>2.769690039828367</v>
+        <v>2.840111856249124</v>
       </c>
       <c r="U65">
         <v>0.0641</v>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>3.163761942940928</v>
+        <v>3.114328162582476</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1099449909068181</v>
+        <v>0.1098607134047382</v>
       </c>
       <c r="C66">
-        <v>7.461241019229307</v>
+        <v>7.301954476359599</v>
       </c>
       <c r="D66">
-        <v>14.4524410192293</v>
+        <v>14.4714544763596</v>
       </c>
       <c r="E66">
-        <v>9.581199999999999</v>
+        <v>9.759499999999999</v>
       </c>
       <c r="F66">
-        <v>11.4112</v>
+        <v>11.5895</v>
       </c>
       <c r="G66">
         <v>4.42</v>
@@ -6687,28 +6687,28 @@
         <v>2.278</v>
       </c>
       <c r="M66">
-        <v>0.73145792</v>
+        <v>0.74288695</v>
       </c>
       <c r="N66">
-        <v>1.54654208</v>
+        <v>1.53511305</v>
       </c>
       <c r="O66">
-        <v>0.309308416</v>
+        <v>0.30702261</v>
       </c>
       <c r="P66">
-        <v>1.237233664</v>
+        <v>1.22809044</v>
       </c>
       <c r="Q66">
-        <v>1.279233664</v>
+        <v>1.27009044</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2142383080744946</v>
+        <v>0.2186534668706806</v>
       </c>
       <c r="T66">
-        <v>2.840111856249124</v>
+        <v>2.914557776465352</v>
       </c>
       <c r="U66">
         <v>0.0641</v>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>3.114328162582476</v>
+        <v>3.066415421619669</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1098607134047382</v>
+        <v>0.1097764359026584</v>
       </c>
       <c r="C67">
-        <v>7.301954476359599</v>
+        <v>7.142718027142353</v>
       </c>
       <c r="D67">
-        <v>14.4714544763596</v>
+        <v>14.49051802714235</v>
       </c>
       <c r="E67">
-        <v>9.759499999999999</v>
+        <v>9.937799999999999</v>
       </c>
       <c r="F67">
-        <v>11.5895</v>
+        <v>11.7678</v>
       </c>
       <c r="G67">
         <v>4.42</v>
@@ -6769,28 +6769,28 @@
         <v>2.278</v>
       </c>
       <c r="M67">
-        <v>0.74288695</v>
+        <v>0.75431598</v>
       </c>
       <c r="N67">
-        <v>1.53511305</v>
+        <v>1.52368402</v>
       </c>
       <c r="O67">
-        <v>0.30702261</v>
+        <v>0.304736804</v>
       </c>
       <c r="P67">
-        <v>1.22809044</v>
+        <v>1.218947216</v>
       </c>
       <c r="Q67">
-        <v>1.27009044</v>
+        <v>1.260947216</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2186534668706806</v>
+        <v>0.2233283408901716</v>
       </c>
       <c r="T67">
-        <v>2.914557776465352</v>
+        <v>2.993382868459006</v>
       </c>
       <c r="U67">
         <v>0.0641</v>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>3.066415421619669</v>
+        <v>3.019954581898159</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1097764359026584</v>
+        <v>0.1138729584005785</v>
       </c>
       <c r="C68">
-        <v>7.142718027142353</v>
+        <v>6.092401671464161</v>
       </c>
       <c r="D68">
-        <v>14.49051802714235</v>
+        <v>13.61850167146416</v>
       </c>
       <c r="E68">
-        <v>9.937799999999999</v>
+        <v>10.1161</v>
       </c>
       <c r="F68">
-        <v>11.7678</v>
+        <v>11.9461</v>
       </c>
       <c r="G68">
         <v>4.42</v>
@@ -6851,45 +6851,45 @@
         <v>2.278</v>
       </c>
       <c r="M68">
-        <v>0.75431598</v>
+        <v>0.85892459</v>
       </c>
       <c r="N68">
-        <v>1.52368402</v>
+        <v>1.41907541</v>
       </c>
       <c r="O68">
-        <v>0.304736804</v>
+        <v>0.283815082</v>
       </c>
       <c r="P68">
-        <v>1.218947216</v>
+        <v>1.135260328</v>
       </c>
       <c r="Q68">
-        <v>1.260947216</v>
+        <v>1.177260328</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2233283408901716</v>
+        <v>0.2282865406078136</v>
       </c>
       <c r="T68">
-        <v>2.993382868459006</v>
+        <v>3.076985238755306</v>
       </c>
       <c r="U68">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V68">
         <v>0.2</v>
       </c>
       <c r="W68">
-        <v>0.05128000000000001</v>
+        <v>0.05752000000000001</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y68">
-        <v>3.019954581898159</v>
+        <v>2.652153665783396</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1138729584005785</v>
+        <v>0.1138510808984986</v>
       </c>
       <c r="C69">
-        <v>6.092401671464161</v>
+        <v>5.918479835553667</v>
       </c>
       <c r="D69">
-        <v>13.61850167146416</v>
+        <v>13.62287983555367</v>
       </c>
       <c r="E69">
-        <v>10.1161</v>
+        <v>10.2944</v>
       </c>
       <c r="F69">
-        <v>11.9461</v>
+        <v>12.1244</v>
       </c>
       <c r="G69">
         <v>4.42</v>
@@ -6933,28 +6933,28 @@
         <v>2.278</v>
       </c>
       <c r="M69">
-        <v>0.85892459</v>
+        <v>0.87174436</v>
       </c>
       <c r="N69">
-        <v>1.41907541</v>
+        <v>1.40625564</v>
       </c>
       <c r="O69">
-        <v>0.283815082</v>
+        <v>0.281251128</v>
       </c>
       <c r="P69">
-        <v>1.135260328</v>
+        <v>1.125004512</v>
       </c>
       <c r="Q69">
-        <v>1.177260328</v>
+        <v>1.167004512</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2282865406078136</v>
+        <v>0.2335546278078082</v>
       </c>
       <c r="T69">
-        <v>3.076985238755306</v>
+        <v>3.165812757195124</v>
       </c>
       <c r="U69">
         <v>0.07190000000000001</v>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.652153665783396</v>
+        <v>2.613151405992463</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1138510808984986</v>
+        <v>0.1138292033964188</v>
       </c>
       <c r="C70">
-        <v>5.918479835553667</v>
+        <v>5.744560815589539</v>
       </c>
       <c r="D70">
-        <v>13.62287983555367</v>
+        <v>13.62726081558954</v>
       </c>
       <c r="E70">
-        <v>10.2944</v>
+        <v>10.4727</v>
       </c>
       <c r="F70">
-        <v>12.1244</v>
+        <v>12.3027</v>
       </c>
       <c r="G70">
         <v>4.42</v>
@@ -7015,28 +7015,28 @@
         <v>2.278</v>
       </c>
       <c r="M70">
-        <v>0.87174436</v>
+        <v>0.88456413</v>
       </c>
       <c r="N70">
-        <v>1.40625564</v>
+        <v>1.39343587</v>
       </c>
       <c r="O70">
-        <v>0.281251128</v>
+        <v>0.278687174</v>
       </c>
       <c r="P70">
-        <v>1.125004512</v>
+        <v>1.114748696</v>
       </c>
       <c r="Q70">
-        <v>1.167004512</v>
+        <v>1.156748696</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2335546278078082</v>
+        <v>0.2391625916013509</v>
       </c>
       <c r="T70">
-        <v>3.165812757195124</v>
+        <v>3.260371083276222</v>
       </c>
       <c r="U70">
         <v>0.07190000000000001</v>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.613151405992463</v>
+        <v>2.575279646485326</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1138292033964188</v>
+        <v>0.1138073258943389</v>
       </c>
       <c r="C71">
-        <v>5.744560815589539</v>
+        <v>5.570644614289387</v>
       </c>
       <c r="D71">
-        <v>13.62726081558954</v>
+        <v>13.63164461428939</v>
       </c>
       <c r="E71">
-        <v>10.4727</v>
+        <v>10.651</v>
       </c>
       <c r="F71">
-        <v>12.3027</v>
+        <v>12.481</v>
       </c>
       <c r="G71">
         <v>4.42</v>
@@ -7097,28 +7097,28 @@
         <v>2.278</v>
       </c>
       <c r="M71">
-        <v>0.88456413</v>
+        <v>0.8973839</v>
       </c>
       <c r="N71">
-        <v>1.39343587</v>
+        <v>1.3806161</v>
       </c>
       <c r="O71">
-        <v>0.278687174</v>
+        <v>0.2761232200000001</v>
       </c>
       <c r="P71">
-        <v>1.114748696</v>
+        <v>1.10449288</v>
       </c>
       <c r="Q71">
-        <v>1.156748696</v>
+        <v>1.14649288</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2391625916013509</v>
+        <v>0.2451444196477964</v>
       </c>
       <c r="T71">
-        <v>3.260371083276222</v>
+        <v>3.361233297762725</v>
       </c>
       <c r="U71">
         <v>0.07190000000000001</v>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.575279646485326</v>
+        <v>2.538489937249822</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1138073258943389</v>
+        <v>0.1137854483922591</v>
       </c>
       <c r="C72">
-        <v>5.570644614289387</v>
+        <v>5.396731234374323</v>
       </c>
       <c r="D72">
-        <v>13.63164461428939</v>
+        <v>13.63603123437432</v>
       </c>
       <c r="E72">
-        <v>10.651</v>
+        <v>10.8293</v>
       </c>
       <c r="F72">
-        <v>12.481</v>
+        <v>12.6593</v>
       </c>
       <c r="G72">
         <v>4.42</v>
@@ -7179,28 +7179,28 @@
         <v>2.278</v>
       </c>
       <c r="M72">
-        <v>0.8973839</v>
+        <v>0.91020367</v>
       </c>
       <c r="N72">
-        <v>1.3806161</v>
+        <v>1.36779633</v>
       </c>
       <c r="O72">
-        <v>0.2761232200000001</v>
+        <v>0.273559266</v>
       </c>
       <c r="P72">
-        <v>1.10449288</v>
+        <v>1.094237064</v>
       </c>
       <c r="Q72">
-        <v>1.14649288</v>
+        <v>1.136237064</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2451444196477964</v>
+        <v>0.251538787559514</v>
       </c>
       <c r="T72">
-        <v>3.361233297762725</v>
+        <v>3.469051527041402</v>
       </c>
       <c r="U72">
         <v>0.07190000000000001</v>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.538489937249822</v>
+        <v>2.502736557851937</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1137854483922591</v>
+        <v>0.1160099708901792</v>
       </c>
       <c r="C73">
-        <v>5.396731234374325</v>
+        <v>4.786389205605303</v>
       </c>
       <c r="D73">
-        <v>13.63603123437432</v>
+        <v>13.2039892056053</v>
       </c>
       <c r="E73">
-        <v>10.8293</v>
+        <v>11.0076</v>
       </c>
       <c r="F73">
-        <v>12.6593</v>
+        <v>12.8376</v>
       </c>
       <c r="G73">
         <v>4.42</v>
@@ -7261,45 +7261,45 @@
         <v>2.278</v>
       </c>
       <c r="M73">
-        <v>0.9102036699999999</v>
+        <v>0.97309008</v>
       </c>
       <c r="N73">
-        <v>1.36779633</v>
+        <v>1.30490992</v>
       </c>
       <c r="O73">
-        <v>0.273559266</v>
+        <v>0.260981984</v>
       </c>
       <c r="P73">
-        <v>1.094237064</v>
+        <v>1.043927936</v>
       </c>
       <c r="Q73">
-        <v>1.136237064</v>
+        <v>1.085927936</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.251538787559514</v>
+        <v>0.2583898960363542</v>
       </c>
       <c r="T73">
-        <v>3.4690515270414</v>
+        <v>3.58457105841141</v>
       </c>
       <c r="U73">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V73">
         <v>0.2</v>
       </c>
       <c r="W73">
-        <v>0.05752000000000001</v>
+        <v>0.06064000000000001</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y73">
-        <v>2.502736557851937</v>
+        <v>2.340996015497352</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1160099708901792</v>
+        <v>0.1160192933880993</v>
       </c>
       <c r="C74">
-        <v>4.786389205605303</v>
+        <v>4.606336209299478</v>
       </c>
       <c r="D74">
-        <v>13.2039892056053</v>
+        <v>13.20223620929948</v>
       </c>
       <c r="E74">
-        <v>11.0076</v>
+        <v>11.1859</v>
       </c>
       <c r="F74">
-        <v>12.8376</v>
+        <v>13.0159</v>
       </c>
       <c r="G74">
         <v>4.42</v>
@@ -7343,28 +7343,28 @@
         <v>2.278</v>
       </c>
       <c r="M74">
-        <v>0.97309008</v>
+        <v>0.9866052199999999</v>
       </c>
       <c r="N74">
-        <v>1.30490992</v>
+        <v>1.29139478</v>
       </c>
       <c r="O74">
-        <v>0.260981984</v>
+        <v>0.258278956</v>
       </c>
       <c r="P74">
-        <v>1.043927936</v>
+        <v>1.033115824</v>
       </c>
       <c r="Q74">
-        <v>1.085927936</v>
+        <v>1.075115824</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2583898960363542</v>
+        <v>0.2657484940299975</v>
       </c>
       <c r="T74">
-        <v>3.58457105841141</v>
+        <v>3.708647592105124</v>
       </c>
       <c r="U74">
         <v>0.07580000000000001</v>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.340996015497352</v>
+        <v>2.308927576928895</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1160192933880993</v>
+        <v>0.1160286158860195</v>
       </c>
       <c r="C75">
-        <v>4.606336209299478</v>
+        <v>4.426283678396658</v>
       </c>
       <c r="D75">
-        <v>13.20223620929948</v>
+        <v>13.20048367839666</v>
       </c>
       <c r="E75">
-        <v>11.1859</v>
+        <v>11.3642</v>
       </c>
       <c r="F75">
-        <v>13.0159</v>
+        <v>13.1942</v>
       </c>
       <c r="G75">
         <v>4.42</v>
@@ -7425,28 +7425,28 @@
         <v>2.278</v>
       </c>
       <c r="M75">
-        <v>0.9866052199999999</v>
+        <v>1.00012036</v>
       </c>
       <c r="N75">
-        <v>1.29139478</v>
+        <v>1.27787964</v>
       </c>
       <c r="O75">
-        <v>0.258278956</v>
+        <v>0.255575928</v>
       </c>
       <c r="P75">
-        <v>1.033115824</v>
+        <v>1.022303712</v>
       </c>
       <c r="Q75">
-        <v>1.075115824</v>
+        <v>1.064303712</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2657484940299975</v>
+        <v>0.2736731380231518</v>
       </c>
       <c r="T75">
-        <v>3.708647592105124</v>
+        <v>3.842268474544509</v>
       </c>
       <c r="U75">
         <v>0.07580000000000001</v>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.308927576928895</v>
+        <v>2.277725852916343</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1160286158860195</v>
+        <v>0.1160379383839396</v>
       </c>
       <c r="C76">
-        <v>4.426283678396658</v>
+        <v>4.246231612711529</v>
       </c>
       <c r="D76">
-        <v>13.20048367839666</v>
+        <v>13.19873161271153</v>
       </c>
       <c r="E76">
-        <v>11.3642</v>
+        <v>11.5425</v>
       </c>
       <c r="F76">
-        <v>13.1942</v>
+        <v>13.3725</v>
       </c>
       <c r="G76">
         <v>4.42</v>
@@ -7507,28 +7507,28 @@
         <v>2.278</v>
       </c>
       <c r="M76">
-        <v>1.00012036</v>
+        <v>1.0136355</v>
       </c>
       <c r="N76">
-        <v>1.27787964</v>
+        <v>1.2643645</v>
       </c>
       <c r="O76">
-        <v>0.255575928</v>
+        <v>0.2528729</v>
       </c>
       <c r="P76">
-        <v>1.022303712</v>
+        <v>1.0114916</v>
       </c>
       <c r="Q76">
-        <v>1.064303712</v>
+        <v>1.0534916</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2736731380231518</v>
+        <v>0.2822317535357585</v>
       </c>
       <c r="T76">
-        <v>3.842268474544509</v>
+        <v>3.986579027579045</v>
       </c>
       <c r="U76">
         <v>0.07580000000000001</v>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.277725852916343</v>
+        <v>2.247356174877459</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1160379383839396</v>
+        <v>0.1160472608818598</v>
       </c>
       <c r="C77">
-        <v>4.246231612711529</v>
+        <v>4.066180012058872</v>
       </c>
       <c r="D77">
-        <v>13.19873161271153</v>
+        <v>13.19698001205887</v>
       </c>
       <c r="E77">
-        <v>11.5425</v>
+        <v>11.7208</v>
       </c>
       <c r="F77">
-        <v>13.3725</v>
+        <v>13.5508</v>
       </c>
       <c r="G77">
         <v>4.42</v>
@@ -7589,28 +7589,28 @@
         <v>2.278</v>
       </c>
       <c r="M77">
-        <v>1.0136355</v>
+        <v>1.02715064</v>
       </c>
       <c r="N77">
-        <v>1.2643645</v>
+        <v>1.25084936</v>
       </c>
       <c r="O77">
-        <v>0.2528729</v>
+        <v>0.250169872</v>
       </c>
       <c r="P77">
-        <v>1.0114916</v>
+        <v>1.000679488</v>
       </c>
       <c r="Q77">
-        <v>1.0534916</v>
+        <v>1.042679488</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2822317535357585</v>
+        <v>0.291503587007749</v>
       </c>
       <c r="T77">
-        <v>3.986579027579045</v>
+        <v>4.142915460033126</v>
       </c>
       <c r="U77">
         <v>0.07580000000000001</v>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.247356174877459</v>
+        <v>2.217785698892229</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1160472608818598</v>
+        <v>0.1160565833797799</v>
       </c>
       <c r="C78">
-        <v>4.066180012058872</v>
+        <v>3.886128876253569</v>
       </c>
       <c r="D78">
-        <v>13.19698001205887</v>
+        <v>13.19522887625357</v>
       </c>
       <c r="E78">
-        <v>11.7208</v>
+        <v>11.8991</v>
       </c>
       <c r="F78">
-        <v>13.5508</v>
+        <v>13.7291</v>
       </c>
       <c r="G78">
         <v>4.42</v>
@@ -7671,28 +7671,28 @@
         <v>2.278</v>
       </c>
       <c r="M78">
-        <v>1.02715064</v>
+        <v>1.04066578</v>
       </c>
       <c r="N78">
-        <v>1.25084936</v>
+        <v>1.23733422</v>
       </c>
       <c r="O78">
-        <v>0.250169872</v>
+        <v>0.247466844</v>
       </c>
       <c r="P78">
-        <v>1.000679488</v>
+        <v>0.989867376</v>
       </c>
       <c r="Q78">
-        <v>1.042679488</v>
+        <v>1.031867376</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.291503587007749</v>
+        <v>0.3015816668686083</v>
       </c>
       <c r="T78">
-        <v>4.142915460033126</v>
+        <v>4.312846364874517</v>
       </c>
       <c r="U78">
         <v>0.07580000000000001</v>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.217785698892229</v>
+        <v>2.188983287218304</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1160565833797799</v>
+        <v>0.1160659058777</v>
       </c>
       <c r="C79">
-        <v>3.886128876253569</v>
+        <v>3.7060782051106</v>
       </c>
       <c r="D79">
-        <v>13.19522887625357</v>
+        <v>13.1934782051106</v>
       </c>
       <c r="E79">
-        <v>11.8991</v>
+        <v>12.0774</v>
       </c>
       <c r="F79">
-        <v>13.7291</v>
+        <v>13.9074</v>
       </c>
       <c r="G79">
         <v>4.42</v>
@@ -7753,28 +7753,28 @@
         <v>2.278</v>
       </c>
       <c r="M79">
-        <v>1.04066578</v>
+        <v>1.05418092</v>
       </c>
       <c r="N79">
-        <v>1.23733422</v>
+        <v>1.22381908</v>
       </c>
       <c r="O79">
-        <v>0.247466844</v>
+        <v>0.244763816</v>
       </c>
       <c r="P79">
-        <v>0.989867376</v>
+        <v>0.979055264</v>
       </c>
       <c r="Q79">
-        <v>1.031867376</v>
+        <v>1.021055264</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3015816668686083</v>
+        <v>0.3125759358077275</v>
       </c>
       <c r="T79">
-        <v>4.312846364874517</v>
+        <v>4.498225533792398</v>
       </c>
       <c r="U79">
         <v>0.07580000000000001</v>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.188983287218304</v>
+        <v>2.160919398920633</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1160659058777</v>
+        <v>0.1160752283756202</v>
       </c>
       <c r="C80">
-        <v>3.7060782051106</v>
+        <v>3.526027998445041</v>
       </c>
       <c r="D80">
-        <v>13.1934782051106</v>
+        <v>13.19172799844504</v>
       </c>
       <c r="E80">
-        <v>12.0774</v>
+        <v>12.2557</v>
       </c>
       <c r="F80">
-        <v>13.9074</v>
+        <v>14.0857</v>
       </c>
       <c r="G80">
         <v>4.42</v>
@@ -7835,28 +7835,28 @@
         <v>2.278</v>
       </c>
       <c r="M80">
-        <v>1.05418092</v>
+        <v>1.06769606</v>
       </c>
       <c r="N80">
-        <v>1.22381908</v>
+        <v>1.21030394</v>
       </c>
       <c r="O80">
-        <v>0.244763816</v>
+        <v>0.242060788</v>
       </c>
       <c r="P80">
-        <v>0.979055264</v>
+        <v>0.968243152</v>
       </c>
       <c r="Q80">
-        <v>1.021055264</v>
+        <v>1.010243152</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3125759358077275</v>
+        <v>0.3246172779791438</v>
       </c>
       <c r="T80">
-        <v>4.498225533792398</v>
+        <v>4.701259861654841</v>
       </c>
       <c r="U80">
         <v>0.07580000000000001</v>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.160919398920633</v>
+        <v>2.133565988807714</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1160752283756202</v>
+        <v>0.1160845508735403</v>
       </c>
       <c r="C81">
-        <v>3.526027998445041</v>
+        <v>3.345978256072073</v>
       </c>
       <c r="D81">
-        <v>13.19172799844504</v>
+        <v>13.18997825607207</v>
       </c>
       <c r="E81">
-        <v>12.2557</v>
+        <v>12.434</v>
       </c>
       <c r="F81">
-        <v>14.0857</v>
+        <v>14.264</v>
       </c>
       <c r="G81">
         <v>4.42</v>
@@ -7917,28 +7917,28 @@
         <v>2.278</v>
       </c>
       <c r="M81">
-        <v>1.06769606</v>
+        <v>1.0812112</v>
       </c>
       <c r="N81">
-        <v>1.21030394</v>
+        <v>1.1967888</v>
       </c>
       <c r="O81">
-        <v>0.242060788</v>
+        <v>0.23935776</v>
       </c>
       <c r="P81">
-        <v>0.968243152</v>
+        <v>0.95743104</v>
       </c>
       <c r="Q81">
-        <v>1.010243152</v>
+        <v>0.99943104</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3246172779791438</v>
+        <v>0.3378627543677017</v>
       </c>
       <c r="T81">
-        <v>4.701259861654841</v>
+        <v>4.924597622303527</v>
       </c>
       <c r="U81">
         <v>0.07580000000000001</v>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.133565988807714</v>
+        <v>2.106896413947617</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1160845508735403</v>
+        <v>0.1160938733714605</v>
       </c>
       <c r="C82">
-        <v>3.345978256072073</v>
+        <v>3.16592897780696</v>
       </c>
       <c r="D82">
-        <v>13.18997825607207</v>
+        <v>13.18822897780696</v>
       </c>
       <c r="E82">
-        <v>12.434</v>
+        <v>12.6123</v>
       </c>
       <c r="F82">
-        <v>14.264</v>
+        <v>14.4423</v>
       </c>
       <c r="G82">
         <v>4.42</v>
@@ -7999,28 +7999,28 @@
         <v>2.278</v>
       </c>
       <c r="M82">
-        <v>1.0812112</v>
+        <v>1.09472634</v>
       </c>
       <c r="N82">
-        <v>1.1967888</v>
+        <v>1.18327366</v>
       </c>
       <c r="O82">
-        <v>0.23935776</v>
+        <v>0.236654732</v>
       </c>
       <c r="P82">
-        <v>0.95743104</v>
+        <v>0.946618928</v>
       </c>
       <c r="Q82">
-        <v>0.99943104</v>
+        <v>0.9886189280000001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3378627543677017</v>
+        <v>0.3525024914287395</v>
       </c>
       <c r="T82">
-        <v>4.924597622303527</v>
+        <v>5.171444620915234</v>
       </c>
       <c r="U82">
         <v>0.07580000000000001</v>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>2.106896413947617</v>
+        <v>2.080885347108758</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1160938733714605</v>
+        <v>0.1161031958693806</v>
       </c>
       <c r="C83">
-        <v>3.16592897780696</v>
+        <v>2.98588016346509</v>
       </c>
       <c r="D83">
-        <v>13.18822897780696</v>
+        <v>13.18648016346509</v>
       </c>
       <c r="E83">
-        <v>12.6123</v>
+        <v>12.7906</v>
       </c>
       <c r="F83">
-        <v>14.4423</v>
+        <v>14.6206</v>
       </c>
       <c r="G83">
         <v>4.42</v>
@@ -8081,28 +8081,28 @@
         <v>2.278</v>
       </c>
       <c r="M83">
-        <v>1.09472634</v>
+        <v>1.10824148</v>
       </c>
       <c r="N83">
-        <v>1.18327366</v>
+        <v>1.16975852</v>
       </c>
       <c r="O83">
-        <v>0.236654732</v>
+        <v>0.233951704</v>
       </c>
       <c r="P83">
-        <v>0.946618928</v>
+        <v>0.935806816</v>
       </c>
       <c r="Q83">
-        <v>0.9886189280000001</v>
+        <v>0.9778068160000001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3525024914287395</v>
+        <v>0.3687688659410035</v>
       </c>
       <c r="T83">
-        <v>5.171444620915234</v>
+        <v>5.445719063817128</v>
       </c>
       <c r="U83">
         <v>0.07580000000000001</v>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.080885347108758</v>
+        <v>2.055508696534261</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1161031958693806</v>
+        <v>0.1161125183673008</v>
       </c>
       <c r="C84">
-        <v>2.98588016346509</v>
+        <v>2.805831812861921</v>
       </c>
       <c r="D84">
-        <v>13.18648016346509</v>
+        <v>13.18473181286192</v>
       </c>
       <c r="E84">
-        <v>12.7906</v>
+        <v>12.9689</v>
       </c>
       <c r="F84">
-        <v>14.6206</v>
+        <v>14.7989</v>
       </c>
       <c r="G84">
         <v>4.42</v>
@@ -8163,28 +8163,28 @@
         <v>2.278</v>
       </c>
       <c r="M84">
-        <v>1.10824148</v>
+        <v>1.12175662</v>
       </c>
       <c r="N84">
-        <v>1.16975852</v>
+        <v>1.15624338</v>
       </c>
       <c r="O84">
-        <v>0.233951704</v>
+        <v>0.231248676</v>
       </c>
       <c r="P84">
-        <v>0.935806816</v>
+        <v>0.9249947040000001</v>
       </c>
       <c r="Q84">
-        <v>0.9778068160000001</v>
+        <v>0.9669947040000001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3687688659410035</v>
+        <v>0.3869489315723575</v>
       </c>
       <c r="T84">
-        <v>5.445719063817128</v>
+        <v>5.752261088236894</v>
       </c>
       <c r="U84">
         <v>0.07580000000000001</v>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>2.055508696534261</v>
+        <v>2.030743531515776</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1161125183673008</v>
+        <v>0.1161218408652209</v>
       </c>
       <c r="C85">
-        <v>2.805831812861921</v>
+        <v>2.625783925813021</v>
       </c>
       <c r="D85">
-        <v>13.18473181286192</v>
+        <v>13.18298392581302</v>
       </c>
       <c r="E85">
-        <v>12.9689</v>
+        <v>13.1472</v>
       </c>
       <c r="F85">
-        <v>14.7989</v>
+        <v>14.9772</v>
       </c>
       <c r="G85">
         <v>4.42</v>
@@ -8245,28 +8245,28 @@
         <v>2.278</v>
       </c>
       <c r="M85">
-        <v>1.12175662</v>
+        <v>1.13527176</v>
       </c>
       <c r="N85">
-        <v>1.15624338</v>
+        <v>1.14272824</v>
       </c>
       <c r="O85">
-        <v>0.231248676</v>
+        <v>0.228545648</v>
       </c>
       <c r="P85">
-        <v>0.9249947040000001</v>
+        <v>0.9141825919999998</v>
       </c>
       <c r="Q85">
-        <v>0.9669947040000001</v>
+        <v>0.9561825919999999</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3869489315723575</v>
+        <v>0.4074015054076308</v>
       </c>
       <c r="T85">
-        <v>5.752261088236894</v>
+        <v>6.09712086570913</v>
       </c>
       <c r="U85">
         <v>0.07580000000000001</v>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.030743531515776</v>
+        <v>2.006568013283445</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1161218408652209</v>
+        <v>0.1257871633631411</v>
       </c>
       <c r="C86">
-        <v>2.625783925813023</v>
+        <v>0.8545059307139251</v>
       </c>
       <c r="D86">
-        <v>13.18298392581302</v>
+        <v>11.59000593071393</v>
       </c>
       <c r="E86">
-        <v>13.1472</v>
+        <v>13.3255</v>
       </c>
       <c r="F86">
-        <v>14.9772</v>
+        <v>15.1555</v>
       </c>
       <c r="G86">
         <v>4.42</v>
@@ -8327,45 +8327,45 @@
         <v>2.278</v>
       </c>
       <c r="M86">
-        <v>1.13527176</v>
+        <v>1.363995</v>
       </c>
       <c r="N86">
-        <v>1.14272824</v>
+        <v>0.9140050000000002</v>
       </c>
       <c r="O86">
-        <v>0.228545648</v>
+        <v>0.182801</v>
       </c>
       <c r="P86">
-        <v>0.9141825920000001</v>
+        <v>0.7312040000000002</v>
       </c>
       <c r="Q86">
-        <v>0.9561825920000001</v>
+        <v>0.7732040000000002</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4074015054076305</v>
+        <v>0.4305810890876069</v>
       </c>
       <c r="T86">
-        <v>6.097120865709127</v>
+        <v>6.487961946844328</v>
       </c>
       <c r="U86">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V86">
         <v>0.2</v>
       </c>
       <c r="W86">
-        <v>0.06064000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y86">
-        <v>2.006568013283445</v>
+        <v>1.670094098585406</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1257871633631411</v>
+        <v>0.1259100858610612</v>
       </c>
       <c r="C87">
-        <v>0.8545059307139251</v>
+        <v>0.6584219967111196</v>
       </c>
       <c r="D87">
-        <v>11.59000593071393</v>
+        <v>11.57222199671112</v>
       </c>
       <c r="E87">
-        <v>13.3255</v>
+        <v>13.5038</v>
       </c>
       <c r="F87">
-        <v>15.1555</v>
+        <v>15.3338</v>
       </c>
       <c r="G87">
         <v>4.42</v>
@@ -8409,28 +8409,28 @@
         <v>2.278</v>
       </c>
       <c r="M87">
-        <v>1.363995</v>
+        <v>1.380042</v>
       </c>
       <c r="N87">
-        <v>0.9140050000000002</v>
+        <v>0.8979580000000003</v>
       </c>
       <c r="O87">
-        <v>0.182801</v>
+        <v>0.1795916000000001</v>
       </c>
       <c r="P87">
-        <v>0.7312040000000002</v>
+        <v>0.7183664000000002</v>
       </c>
       <c r="Q87">
-        <v>0.7732040000000002</v>
+        <v>0.7603664000000002</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4305810890876069</v>
+        <v>0.4570720418647227</v>
       </c>
       <c r="T87">
-        <v>6.487961946844328</v>
+        <v>6.9346374681417</v>
       </c>
       <c r="U87">
         <v>0.09</v>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>1.670094098585406</v>
+        <v>1.650674399764645</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1259100858610612</v>
+        <v>0.1260330083589813</v>
       </c>
       <c r="C88">
-        <v>0.6584219967111196</v>
+        <v>0.4623925551331869</v>
       </c>
       <c r="D88">
-        <v>11.57222199671112</v>
+        <v>11.55449255513319</v>
       </c>
       <c r="E88">
-        <v>13.5038</v>
+        <v>13.6821</v>
       </c>
       <c r="F88">
-        <v>15.3338</v>
+        <v>15.5121</v>
       </c>
       <c r="G88">
         <v>4.42</v>
@@ -8491,28 +8491,28 @@
         <v>2.278</v>
       </c>
       <c r="M88">
-        <v>1.380042</v>
+        <v>1.396089</v>
       </c>
       <c r="N88">
-        <v>0.8979580000000003</v>
+        <v>0.8819110000000001</v>
       </c>
       <c r="O88">
-        <v>0.1795916000000001</v>
+        <v>0.1763822</v>
       </c>
       <c r="P88">
-        <v>0.7183664000000002</v>
+        <v>0.7055288000000001</v>
       </c>
       <c r="Q88">
-        <v>0.7603664000000002</v>
+        <v>0.7475288000000001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4570720418647227</v>
+        <v>0.4876385258383178</v>
       </c>
       <c r="T88">
-        <v>6.9346374681417</v>
+        <v>7.450032300407898</v>
       </c>
       <c r="U88">
         <v>0.09</v>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>1.650674399764645</v>
+        <v>1.631701130801833</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1260330083589813</v>
+        <v>0.1261559308569015</v>
       </c>
       <c r="C89">
-        <v>0.4623925551331869</v>
+        <v>0.2664173559048191</v>
       </c>
       <c r="D89">
-        <v>11.55449255513319</v>
+        <v>11.53681735590482</v>
       </c>
       <c r="E89">
-        <v>13.6821</v>
+        <v>13.8604</v>
       </c>
       <c r="F89">
-        <v>15.5121</v>
+        <v>15.6904</v>
       </c>
       <c r="G89">
         <v>4.42</v>
@@ -8573,28 +8573,28 @@
         <v>2.278</v>
       </c>
       <c r="M89">
-        <v>1.396089</v>
+        <v>1.412136</v>
       </c>
       <c r="N89">
-        <v>0.8819110000000001</v>
+        <v>0.8658640000000002</v>
       </c>
       <c r="O89">
-        <v>0.1763822</v>
+        <v>0.1731728</v>
       </c>
       <c r="P89">
-        <v>0.7055288000000001</v>
+        <v>0.6926912000000002</v>
       </c>
       <c r="Q89">
-        <v>0.7475288000000001</v>
+        <v>0.7346912000000002</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4876385258383178</v>
+        <v>0.5232994238075123</v>
       </c>
       <c r="T89">
-        <v>7.450032300407898</v>
+        <v>8.051326271385131</v>
       </c>
       <c r="U89">
         <v>0.09</v>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>1.631701130801833</v>
+        <v>1.613159072497267</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1261559308569015</v>
+        <v>0.1262788533548216</v>
       </c>
       <c r="C90">
-        <v>0.2664173559048191</v>
+        <v>0.07049615047854907</v>
       </c>
       <c r="D90">
-        <v>11.53681735590482</v>
+        <v>11.51919615047855</v>
       </c>
       <c r="E90">
-        <v>13.8604</v>
+        <v>14.0387</v>
       </c>
       <c r="F90">
-        <v>15.6904</v>
+        <v>15.8687</v>
       </c>
       <c r="G90">
         <v>4.42</v>
@@ -8655,28 +8655,28 @@
         <v>2.278</v>
       </c>
       <c r="M90">
-        <v>1.412136</v>
+        <v>1.428183</v>
       </c>
       <c r="N90">
-        <v>0.8658640000000002</v>
+        <v>0.8498170000000003</v>
       </c>
       <c r="O90">
-        <v>0.1731728</v>
+        <v>0.1699634000000001</v>
       </c>
       <c r="P90">
-        <v>0.6926912000000002</v>
+        <v>0.6798536000000002</v>
       </c>
       <c r="Q90">
-        <v>0.7346912000000002</v>
+        <v>0.7218536000000002</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5232994238075123</v>
+        <v>0.5654441214074691</v>
       </c>
       <c r="T90">
-        <v>8.051326271385131</v>
+        <v>8.761946418903678</v>
       </c>
       <c r="U90">
         <v>0.09</v>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>1.613159072497267</v>
+        <v>1.595033689660219</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1262788533548216</v>
+        <v>0.1264017758527418</v>
       </c>
       <c r="C91">
-        <v>0.07049615047854907</v>
+        <v>-0.1253713081769092</v>
       </c>
       <c r="D91">
-        <v>11.51919615047855</v>
+        <v>11.50162869182309</v>
       </c>
       <c r="E91">
-        <v>14.0387</v>
+        <v>14.217</v>
       </c>
       <c r="F91">
-        <v>15.8687</v>
+        <v>16.047</v>
       </c>
       <c r="G91">
         <v>4.42</v>
@@ -8737,28 +8737,28 @@
         <v>2.278</v>
       </c>
       <c r="M91">
-        <v>1.428183</v>
+        <v>1.44423</v>
       </c>
       <c r="N91">
-        <v>0.8498170000000003</v>
+        <v>0.8337700000000001</v>
       </c>
       <c r="O91">
-        <v>0.1699634000000001</v>
+        <v>0.166754</v>
       </c>
       <c r="P91">
-        <v>0.6798536000000002</v>
+        <v>0.6670160000000001</v>
       </c>
       <c r="Q91">
-        <v>0.7218536000000002</v>
+        <v>0.7090160000000001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5654441214074691</v>
+        <v>0.6160177585274177</v>
       </c>
       <c r="T91">
-        <v>8.761946418903678</v>
+        <v>9.614690595925936</v>
       </c>
       <c r="U91">
         <v>0.09</v>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>1.595033689660219</v>
+        <v>1.577311093108439</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1264017758527418</v>
+        <v>0.1265246983506619</v>
       </c>
       <c r="C92">
-        <v>-0.1253713081769092</v>
+        <v>-0.3211852655881469</v>
       </c>
       <c r="D92">
-        <v>11.50162869182309</v>
+        <v>11.48411473441185</v>
       </c>
       <c r="E92">
-        <v>14.217</v>
+        <v>14.3953</v>
       </c>
       <c r="F92">
-        <v>16.047</v>
+        <v>16.2253</v>
       </c>
       <c r="G92">
         <v>4.42</v>
@@ -8819,28 +8819,28 @@
         <v>2.278</v>
       </c>
       <c r="M92">
-        <v>1.44423</v>
+        <v>1.460277</v>
       </c>
       <c r="N92">
-        <v>0.8337700000000001</v>
+        <v>0.817723</v>
       </c>
       <c r="O92">
-        <v>0.166754</v>
+        <v>0.1635446</v>
       </c>
       <c r="P92">
-        <v>0.6670160000000001</v>
+        <v>0.6541783999999999</v>
       </c>
       <c r="Q92">
-        <v>0.7090160000000001</v>
+        <v>0.6961784</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6160177585274177</v>
+        <v>0.6778299816740212</v>
       </c>
       <c r="T92">
-        <v>9.614690595925936</v>
+        <v>10.65693347895314</v>
       </c>
       <c r="U92">
         <v>0.09</v>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>1.577311093108439</v>
+        <v>1.559978004173181</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1265246983506619</v>
+        <v>0.126647620848582</v>
       </c>
       <c r="C93">
-        <v>-0.3211852655881469</v>
+        <v>-0.5169459657885831</v>
       </c>
       <c r="D93">
-        <v>11.48411473441185</v>
+        <v>11.46665403421142</v>
       </c>
       <c r="E93">
-        <v>14.3953</v>
+        <v>14.5736</v>
       </c>
       <c r="F93">
-        <v>16.2253</v>
+        <v>16.4036</v>
       </c>
       <c r="G93">
         <v>4.42</v>
@@ -8901,28 +8901,28 @@
         <v>2.278</v>
       </c>
       <c r="M93">
-        <v>1.460277</v>
+        <v>1.476324</v>
       </c>
       <c r="N93">
-        <v>0.817723</v>
+        <v>0.8016760000000001</v>
       </c>
       <c r="O93">
-        <v>0.1635446</v>
+        <v>0.1603352</v>
       </c>
       <c r="P93">
-        <v>0.6541783999999999</v>
+        <v>0.6413408</v>
       </c>
       <c r="Q93">
-        <v>0.6961784</v>
+        <v>0.6833408000000001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6778299816740212</v>
+        <v>0.7550952606072757</v>
       </c>
       <c r="T93">
-        <v>10.65693347895314</v>
+        <v>11.95973708273714</v>
       </c>
       <c r="U93">
         <v>0.09</v>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>1.559978004173181</v>
+        <v>1.543021721519124</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.126647620848582</v>
+        <v>0.1267705433465022</v>
       </c>
       <c r="C94">
-        <v>-0.5169459657885831</v>
+        <v>-0.7126536513297239</v>
       </c>
       <c r="D94">
-        <v>11.46665403421142</v>
+        <v>11.44924634867028</v>
       </c>
       <c r="E94">
-        <v>14.5736</v>
+        <v>14.7519</v>
       </c>
       <c r="F94">
-        <v>16.4036</v>
+        <v>16.5819</v>
       </c>
       <c r="G94">
         <v>4.42</v>
@@ -8983,28 +8983,28 @@
         <v>2.278</v>
       </c>
       <c r="M94">
-        <v>1.476324</v>
+        <v>1.492371</v>
       </c>
       <c r="N94">
-        <v>0.8016760000000001</v>
+        <v>0.7856289999999999</v>
       </c>
       <c r="O94">
-        <v>0.1603352</v>
+        <v>0.1571258</v>
       </c>
       <c r="P94">
-        <v>0.6413408</v>
+        <v>0.6285031999999999</v>
       </c>
       <c r="Q94">
-        <v>0.6833408000000001</v>
+        <v>0.6705032</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7550952606072757</v>
+        <v>0.8544363335214602</v>
       </c>
       <c r="T94">
-        <v>11.95973708273714</v>
+        <v>13.63477028760229</v>
       </c>
       <c r="U94">
         <v>0.09</v>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>1.543021721519124</v>
+        <v>1.52643009010494</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1267705433465022</v>
+        <v>0.1268934658444223</v>
       </c>
       <c r="C95">
-        <v>-0.7126536513297239</v>
+        <v>-0.9083085632924437</v>
       </c>
       <c r="D95">
-        <v>11.44924634867028</v>
+        <v>11.43189143670756</v>
       </c>
       <c r="E95">
-        <v>14.7519</v>
+        <v>14.9302</v>
       </c>
       <c r="F95">
-        <v>16.5819</v>
+        <v>16.7602</v>
       </c>
       <c r="G95">
         <v>4.42</v>
@@ -9065,28 +9065,28 @@
         <v>2.278</v>
       </c>
       <c r="M95">
-        <v>1.492371</v>
+        <v>1.508418</v>
       </c>
       <c r="N95">
-        <v>0.7856289999999999</v>
+        <v>0.769582</v>
       </c>
       <c r="O95">
-        <v>0.1571258</v>
+        <v>0.1539164</v>
       </c>
       <c r="P95">
-        <v>0.6285031999999999</v>
+        <v>0.6156656</v>
       </c>
       <c r="Q95">
-        <v>0.6705032</v>
+        <v>0.6576656000000001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.8544363335214602</v>
+        <v>0.9868910974070394</v>
       </c>
       <c r="T95">
-        <v>13.63477028760229</v>
+        <v>15.86814789408915</v>
       </c>
       <c r="U95">
         <v>0.09</v>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>1.52643009010494</v>
+        <v>1.510191472125101</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1268934658444223</v>
+        <v>0.1736321918265164</v>
       </c>
       <c r="C96">
-        <v>-0.9083085632924437</v>
+        <v>-5.26640109976438</v>
       </c>
       <c r="D96">
-        <v>11.43189143670756</v>
+        <v>7.25209890023562</v>
       </c>
       <c r="E96">
-        <v>14.9302</v>
+        <v>15.1085</v>
       </c>
       <c r="F96">
-        <v>16.7602</v>
+        <v>16.9385</v>
       </c>
       <c r="G96">
         <v>4.42</v>
@@ -9147,45 +9147,45 @@
         <v>2.278</v>
       </c>
       <c r="M96">
-        <v>1.508418</v>
+        <v>2.486571800000001</v>
       </c>
       <c r="N96">
-        <v>0.769582</v>
+        <v>-0.2085718000000005</v>
       </c>
       <c r="O96">
-        <v>0.1539164</v>
+        <v>-0.04171436000000011</v>
       </c>
       <c r="P96">
-        <v>0.6156656</v>
+        <v>-0.1668574400000004</v>
       </c>
       <c r="Q96">
-        <v>0.6576656000000001</v>
+        <v>-0.1248574400000004</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.9868910974070394</v>
+        <v>1.194492630697462</v>
       </c>
       <c r="T96">
-        <v>15.86814789408915</v>
+        <v>19.36860799021445</v>
       </c>
       <c r="U96">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V96">
-        <v>0.2</v>
+        <v>0.1832241482027585</v>
       </c>
       <c r="W96">
-        <v>0.07199999999999999</v>
+        <v>0.1199026950438351</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y96">
-        <v>1.510191472125101</v>
+        <v>0.9161207410137924</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1736321918265164</v>
+        <v>0.1746421918265163</v>
       </c>
       <c r="C97">
-        <v>-5.26640109976438</v>
+        <v>-5.501550644043324</v>
       </c>
       <c r="D97">
-        <v>7.25209890023562</v>
+        <v>7.195249355956677</v>
       </c>
       <c r="E97">
-        <v>15.1085</v>
+        <v>15.2868</v>
       </c>
       <c r="F97">
-        <v>16.9385</v>
+        <v>17.1168</v>
       </c>
       <c r="G97">
         <v>4.42</v>
@@ -9229,37 +9229,37 @@
         <v>2.278</v>
       </c>
       <c r="M97">
-        <v>2.486571800000001</v>
+        <v>2.51274624</v>
       </c>
       <c r="N97">
-        <v>-0.2085718000000005</v>
+        <v>-0.2347462400000002</v>
       </c>
       <c r="O97">
-        <v>-0.04171436000000011</v>
+        <v>-0.04694924800000005</v>
       </c>
       <c r="P97">
-        <v>-0.1668574400000004</v>
+        <v>-0.1877969920000002</v>
       </c>
       <c r="Q97">
-        <v>-0.1248574400000004</v>
+        <v>-0.1457969920000002</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.194492630697462</v>
+        <v>1.481665788371828</v>
       </c>
       <c r="T97">
-        <v>19.36860799021445</v>
+        <v>24.21075998776806</v>
       </c>
       <c r="U97">
         <v>0.1468</v>
       </c>
       <c r="V97">
-        <v>0.1832241482027585</v>
+        <v>0.1813155633256464</v>
       </c>
       <c r="W97">
-        <v>0.1199026950438351</v>
+        <v>0.1201828753037951</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.9161207410137924</v>
+        <v>0.9065778166282321</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1746421918265163</v>
+        <v>0.1756521918265163</v>
       </c>
       <c r="C98">
-        <v>-5.50155064404332</v>
+        <v>-5.735815828360156</v>
       </c>
       <c r="D98">
-        <v>7.195249355956677</v>
+        <v>7.139284171639841</v>
       </c>
       <c r="E98">
-        <v>15.2868</v>
+        <v>15.4651</v>
       </c>
       <c r="F98">
-        <v>17.1168</v>
+        <v>17.2951</v>
       </c>
       <c r="G98">
         <v>4.42</v>
@@ -9311,37 +9311,37 @@
         <v>2.278</v>
       </c>
       <c r="M98">
-        <v>2.51274624</v>
+        <v>2.53892068</v>
       </c>
       <c r="N98">
-        <v>-0.2347462399999998</v>
+        <v>-0.2609206799999999</v>
       </c>
       <c r="O98">
-        <v>-0.04694924799999996</v>
+        <v>-0.05218413599999999</v>
       </c>
       <c r="P98">
-        <v>-0.1877969919999998</v>
+        <v>-0.2087365439999999</v>
       </c>
       <c r="Q98">
-        <v>-0.1457969919999998</v>
+        <v>-0.1667365439999999</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.481665788371824</v>
+        <v>1.960287717829099</v>
       </c>
       <c r="T98">
-        <v>24.210759987768</v>
+        <v>32.281013317024</v>
       </c>
       <c r="U98">
         <v>0.1468</v>
       </c>
       <c r="V98">
-        <v>0.1813155633256465</v>
+        <v>0.1794463307140419</v>
       </c>
       <c r="W98">
-        <v>0.1201828753037951</v>
+        <v>0.1204572786511787</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.9065778166282323</v>
+        <v>0.8972316535702093</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1756521918265163</v>
+        <v>0.1766621918265164</v>
       </c>
       <c r="C99">
-        <v>-5.735815828360156</v>
+        <v>-5.969217129299054</v>
       </c>
       <c r="D99">
-        <v>7.139284171639841</v>
+        <v>7.084182870700944</v>
       </c>
       <c r="E99">
-        <v>15.4651</v>
+        <v>15.6434</v>
       </c>
       <c r="F99">
-        <v>17.2951</v>
+        <v>17.4734</v>
       </c>
       <c r="G99">
         <v>4.42</v>
@@ -9393,37 +9393,37 @@
         <v>2.278</v>
       </c>
       <c r="M99">
-        <v>2.53892068</v>
+        <v>2.56509512</v>
       </c>
       <c r="N99">
-        <v>-0.2609206799999999</v>
+        <v>-0.28709512</v>
       </c>
       <c r="O99">
-        <v>-0.05218413599999999</v>
+        <v>-0.05741902400000001</v>
       </c>
       <c r="P99">
-        <v>-0.2087365439999999</v>
+        <v>-0.229676096</v>
       </c>
       <c r="Q99">
-        <v>-0.1667365439999999</v>
+        <v>-0.187676096</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.960287717829099</v>
+        <v>2.917531576743649</v>
       </c>
       <c r="T99">
-        <v>32.281013317024</v>
+        <v>48.421519975536</v>
       </c>
       <c r="U99">
         <v>0.1468</v>
       </c>
       <c r="V99">
-        <v>0.1794463307140419</v>
+        <v>0.1776152457067557</v>
       </c>
       <c r="W99">
-        <v>0.1204572786511787</v>
+        <v>0.1207260819302483</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.8972316535702093</v>
+        <v>0.8880762285337784</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1766621918265164</v>
+        <v>0.1776721918265163</v>
       </c>
       <c r="C100">
-        <v>-5.969217129299054</v>
+        <v>-6.201774396129203</v>
       </c>
       <c r="D100">
-        <v>7.084182870700944</v>
+        <v>7.029925603870796</v>
       </c>
       <c r="E100">
-        <v>15.6434</v>
+        <v>15.8217</v>
       </c>
       <c r="F100">
-        <v>17.4734</v>
+        <v>17.6517</v>
       </c>
       <c r="G100">
         <v>4.42</v>
@@ -9475,37 +9475,37 @@
         <v>2.278</v>
       </c>
       <c r="M100">
-        <v>2.56509512</v>
+        <v>2.59126956</v>
       </c>
       <c r="N100">
-        <v>-0.28709512</v>
+        <v>-0.3132695600000002</v>
       </c>
       <c r="O100">
-        <v>-0.05741902400000001</v>
+        <v>-0.06265391200000003</v>
       </c>
       <c r="P100">
-        <v>-0.229676096</v>
+        <v>-0.2506156480000001</v>
       </c>
       <c r="Q100">
-        <v>-0.187676096</v>
+        <v>-0.2086156480000001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.917531576743649</v>
+        <v>5.789263153487298</v>
       </c>
       <c r="T100">
-        <v>48.421519975536</v>
+        <v>96.843039951072</v>
       </c>
       <c r="U100">
         <v>0.1468</v>
       </c>
       <c r="V100">
-        <v>0.1776152457067557</v>
+        <v>0.1758211523157784</v>
       </c>
       <c r="W100">
-        <v>0.1207260819302483</v>
+        <v>0.1209894548400438</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.8880762285337784</v>
+        <v>0.8791057615788918</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1776721918265163</v>
-      </c>
-      <c r="C101">
-        <v>-6.201774396129203</v>
-      </c>
-      <c r="D101">
-        <v>7.029925603870796</v>
-      </c>
-      <c r="E101">
-        <v>15.8217</v>
-      </c>
-      <c r="F101">
-        <v>17.6517</v>
-      </c>
-      <c r="G101">
-        <v>4.42</v>
-      </c>
-      <c r="H101">
-        <v>16</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>2.32</v>
-      </c>
-      <c r="K101">
-        <v>0.042</v>
-      </c>
-      <c r="L101">
-        <v>2.278</v>
-      </c>
-      <c r="M101">
-        <v>2.59126956</v>
-      </c>
-      <c r="N101">
-        <v>-0.3132695600000002</v>
-      </c>
-      <c r="O101">
-        <v>-0.06265391200000003</v>
-      </c>
-      <c r="P101">
-        <v>-0.2506156480000001</v>
-      </c>
-      <c r="Q101">
-        <v>-0.2086156480000001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.789263153487298</v>
-      </c>
-      <c r="T101">
-        <v>96.843039951072</v>
-      </c>
-      <c r="U101">
-        <v>0.1468</v>
-      </c>
-      <c r="V101">
-        <v>0.1758211523157784</v>
-      </c>
-      <c r="W101">
-        <v>0.1209894548400438</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ca2/CC</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.8791057615788918</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
